--- a/reports/2026-03-17.xlsx
+++ b/reports/2026-03-17.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trade Candidates'!$A$1:$AG$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Enter Candidates'!$A$1:$AG$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wait Candidates'!$A$1:$AG$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Enter Candidates'!$A$1:$AG$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wait Candidates'!$A$1:$AG$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-17 05:37 UTC</t>
+          <t>2026-03-17 15:51 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -642,7 +642,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-03-17_1773725740685</t>
+          <t>2026-03-17_1773762595579</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>entry_chased</t>
+          <t>entry_late</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -956,14 +956,14 @@
         <v>3.570573042426071e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>3.802e-06</v>
+        <v>3.633e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.481507444997758</v>
+        <v>1.748373631687761</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>chased</t>
+          <t>late</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -988,22 +988,22 @@
         <v>2.000000000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.07883326763894954</v>
+        <v>0.02752167331772813</v>
       </c>
       <c r="AA2" t="n">
-        <v>281035.212427225</v>
+        <v>831628.6260935001</v>
       </c>
       <c r="AB2" t="n">
-        <v>303972.512402603</v>
+        <v>568280.167103815</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.822627000000001</v>
+        <v>9.201302</v>
       </c>
       <c r="AD2" t="n">
-        <v>15.65917</v>
+        <v>14.914928</v>
       </c>
       <c r="AE2" t="n">
-        <v>1574788786.790929</v>
+        <v>1503762547.232597</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -1018,22 +1018,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SUIUSDT</t>
+          <t>TRXUSDT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sui</t>
+          <t>TRON</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ENTER</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>entry_chased</t>
+          <t>effective_rr_insufficient | entry_chased</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65.864</v>
+        <v>74.752</v>
       </c>
       <c r="I3" t="n">
-        <v>82.33</v>
+        <v>93.44</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -1070,13 +1070,13 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9740674814932353</v>
+        <v>0.2893153896519431</v>
       </c>
       <c r="P3" t="n">
-        <v>1.029</v>
+        <v>0.3042</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.639498243238106</v>
+        <v>5.144769646012826</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -1084,43 +1084,43 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0.789</v>
+        <v>0.268</v>
       </c>
       <c r="T3" t="n">
-        <v>18.99945178433929</v>
+        <v>7.367527070573851</v>
       </c>
       <c r="U3" t="n">
-        <v>1.15913496298647</v>
+        <v>0.3106307793038863</v>
       </c>
       <c r="V3" t="n">
-        <v>1.344202444479706</v>
+        <v>0.3319461689558294</v>
       </c>
       <c r="W3" t="n">
-        <v>1.529269925972941</v>
+        <v>0.3532615586077725</v>
       </c>
       <c r="X3" t="n">
-        <v>0.9999999999999994</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
         <v>2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.009708266588999464</v>
+        <v>0.03287851389118675</v>
       </c>
       <c r="AA3" t="n">
-        <v>313244.558082</v>
+        <v>1529175.661605</v>
       </c>
       <c r="AB3" t="n">
-        <v>346435.702239</v>
+        <v>967099.6149340001</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.700078</v>
+        <v>1.643926</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.358873</v>
+        <v>1.643926</v>
       </c>
       <c r="AE3" t="n">
-        <v>4021498012.456191</v>
+        <v>28807874085.95885</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
@@ -1135,22 +1135,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XLMUSDT</t>
+          <t>SUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ENTER</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>entry_chased</t>
+          <t>tradeability_marginal | entry_chased</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>64.44799999999999</v>
+        <v>73.032</v>
       </c>
       <c r="I4" t="n">
-        <v>80.56</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -1175,25 +1175,25 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N4" t="b">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1615448108821275</v>
+        <v>0.04320432927693411</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1739</v>
+        <v>0.04854</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.648149792250214</v>
+        <v>12.34985199947196</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1201,19 +1201,19 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0.1362</v>
+        <v>0.03667</v>
       </c>
       <c r="T4" t="n">
-        <v>15.6890281673118</v>
+        <v>15.12424654263213</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1868896217642551</v>
+        <v>0.04973865855386821</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2122344326463827</v>
+        <v>0.05627298783080232</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2375792435285102</v>
+        <v>0.06280731710773643</v>
       </c>
       <c r="X4" t="n">
         <v>1</v>
@@ -1222,22 +1222,22 @@
         <v>2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.05752085130859303</v>
+        <v>0.02058672156458286</v>
       </c>
       <c r="AA4" t="n">
-        <v>195551.569347</v>
+        <v>19553.5759032</v>
       </c>
       <c r="AB4" t="n">
-        <v>260127.512412</v>
+        <v>13143.0154511</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.876043</v>
+        <v>15.154426</v>
       </c>
       <c r="AD4" t="n">
-        <v>8.243309999999999</v>
+        <v>354.823323</v>
       </c>
       <c r="AE4" t="n">
-        <v>5748011796.422249</v>
+        <v>139858424.4330002</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
@@ -1252,22 +1252,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LTCUSDT</t>
+          <t>ZENUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Horizen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ENTER</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>entry_chased</t>
+          <t>tradeability_marginal | entry_chased</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>64.06399999999999</v>
+        <v>72.104</v>
       </c>
       <c r="I5" t="n">
-        <v>80.08</v>
+        <v>90.13</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -1292,25 +1292,25 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N5" t="b">
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>55.19368745876001</v>
+        <v>5.764233529855139</v>
       </c>
       <c r="P5" t="n">
-        <v>57.86</v>
+        <v>6.619</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.83082878496246</v>
+        <v>14.82879667726338</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1318,19 +1318,19 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>45</v>
+        <v>4.94</v>
       </c>
       <c r="T5" t="n">
-        <v>18.46893717035412</v>
+        <v>14.29910022878363</v>
       </c>
       <c r="U5" t="n">
-        <v>65.38737491752002</v>
+        <v>6.588467059710278</v>
       </c>
       <c r="V5" t="n">
-        <v>75.58106237628003</v>
+        <v>7.412700589565417</v>
       </c>
       <c r="W5" t="n">
-        <v>85.77474983504004</v>
+        <v>8.236934119420557</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
@@ -1339,22 +1339,22 @@
         <v>2</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01727861771059199</v>
+        <v>0.03019323671497252</v>
       </c>
       <c r="AA5" t="n">
-        <v>421843.257056</v>
+        <v>7487.28291</v>
       </c>
       <c r="AB5" t="n">
-        <v>254673.128187</v>
+        <v>7368.29412</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.95594</v>
+        <v>18.150932</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.323295</v>
+        <v>410.330327</v>
       </c>
       <c r="AE5" t="n">
-        <v>4453487185.845181</v>
+        <v>118483517.806406</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CROUSDT</t>
+          <t>REZUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cronos</t>
+          <t>Renzo</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>76.65600000000001</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>95.81999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
@@ -1421,13 +1421,13 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.07706222520171957</v>
+        <v>0.003302794856571019</v>
       </c>
       <c r="P6" t="n">
-        <v>0.07964</v>
+        <v>0.003496</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.345056273073865</v>
+        <v>5.849747011825235</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1435,43 +1435,43 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>0.06811</v>
+        <v>0.002644</v>
       </c>
       <c r="T6" t="n">
-        <v>11.61687866952459</v>
+        <v>19.94658721416878</v>
       </c>
       <c r="U6" t="n">
-        <v>0.08601445040343914</v>
+        <v>0.003961589713142038</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0949666756051587</v>
+        <v>0.004620384569713056</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1039189008068783</v>
+        <v>0.005279179426284076</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>2</v>
+        <v>1.999999999999999</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.08790104853393685</v>
+        <v>0.171624713958808</v>
       </c>
       <c r="AA6" t="n">
-        <v>8513.6971428</v>
+        <v>15379.33683327</v>
       </c>
       <c r="AB6" t="n">
-        <v>7202.0159494</v>
+        <v>10728.90403699</v>
       </c>
       <c r="AC6" t="n">
-        <v>32.753152</v>
+        <v>20.545616</v>
       </c>
       <c r="AD6" t="n">
-        <v>365.165237</v>
+        <v>92.307366</v>
       </c>
       <c r="AE6" t="n">
-        <v>3285511403.793965</v>
+        <v>27258722.09736478</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
@@ -1515,10 +1515,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>74.44</v>
+        <v>70.328</v>
       </c>
       <c r="I7" t="n">
-        <v>93.05</v>
+        <v>87.91</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
@@ -1541,10 +1541,10 @@
         <v>0.03091180535852996</v>
       </c>
       <c r="P7" t="n">
-        <v>0.035</v>
+        <v>0.035605</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.22535061945815</v>
+        <v>15.18253168016592</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1573,22 +1573,22 @@
         <v>1.999999999999999</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1002822228271</v>
+        <v>0.1289382217737537</v>
       </c>
       <c r="AA7" t="n">
-        <v>42900.87676025</v>
+        <v>55967.13071129</v>
       </c>
       <c r="AB7" t="n">
-        <v>11873.70124821</v>
+        <v>20457.86793545</v>
       </c>
       <c r="AC7" t="n">
-        <v>11.450943</v>
+        <v>26.682585</v>
       </c>
       <c r="AD7" t="n">
-        <v>66.481675</v>
+        <v>51.172304</v>
       </c>
       <c r="AE7" t="n">
-        <v>957875665.1243513</v>
+        <v>975806733.049776</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
@@ -1603,12 +1603,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SUSDT</t>
+          <t>ZECUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>Zcash</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_chased</t>
+          <t>effective_rr_insufficient | entry_chased</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>73.032</v>
+        <v>68.792</v>
       </c>
       <c r="I8" t="n">
-        <v>91.29000000000001</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
@@ -1643,25 +1643,25 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N8" t="b">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04320432927693411</v>
+        <v>229.6644212431871</v>
       </c>
       <c r="P8" t="n">
-        <v>0.04822</v>
+        <v>268.65</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.60918548443628</v>
+        <v>16.97501883216464</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1669,19 +1669,19 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>0.03667</v>
+        <v>185</v>
       </c>
       <c r="T8" t="n">
-        <v>15.12424654263213</v>
+        <v>19.44768850195251</v>
       </c>
       <c r="U8" t="n">
-        <v>0.04973865855386821</v>
+        <v>274.3288424863741</v>
       </c>
       <c r="V8" t="n">
-        <v>0.05627298783080232</v>
+        <v>318.9932637295612</v>
       </c>
       <c r="W8" t="n">
-        <v>0.06280731710773643</v>
+        <v>363.6576849727483</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
@@ -1690,22 +1690,22 @@
         <v>2</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.02074904035688985</v>
+        <v>0.003721691881125777</v>
       </c>
       <c r="AA8" t="n">
-        <v>17296.7617039</v>
+        <v>117906.88669995</v>
       </c>
       <c r="AB8" t="n">
-        <v>25089.7056129</v>
+        <v>71126.95808521</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.178</v>
+        <v>7.961808</v>
       </c>
       <c r="AD8" t="n">
-        <v>24.494745</v>
+        <v>11.554508</v>
       </c>
       <c r="AE8" t="n">
-        <v>139100289.1268733</v>
+        <v>4445895174.543806</v>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
@@ -1720,12 +1720,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ZENUSDT</t>
+          <t>MEUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Horizen</t>
+          <t>Magic Eden</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_chased</t>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1749,15 +1749,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>72.104</v>
+        <v>67.384</v>
       </c>
       <c r="I9" t="n">
-        <v>90.13</v>
+        <v>84.23</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>none</t>
@@ -1772,13 +1776,13 @@
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>5.764233529855139</v>
+        <v>0.1190546835514273</v>
       </c>
       <c r="P9" t="n">
-        <v>6.623</v>
+        <v>0.1228</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.89819011837368</v>
+        <v>3.145879134570029</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1786,19 +1790,19 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>4.94</v>
+        <v>0.1106</v>
       </c>
       <c r="T9" t="n">
-        <v>14.29910022878363</v>
+        <v>7.101512766421464</v>
       </c>
       <c r="U9" t="n">
-        <v>6.588467059710278</v>
+        <v>0.1275093671028546</v>
       </c>
       <c r="V9" t="n">
-        <v>7.412700589565417</v>
+        <v>0.1359640506542819</v>
       </c>
       <c r="W9" t="n">
-        <v>8.236934119420557</v>
+        <v>0.1444187342057091</v>
       </c>
       <c r="X9" t="n">
         <v>1</v>
@@ -1807,22 +1811,22 @@
         <v>2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0453137980515084</v>
+        <v>0.08146639511201863</v>
       </c>
       <c r="AA9" t="n">
-        <v>6939.51449</v>
+        <v>12477.055833</v>
       </c>
       <c r="AB9" t="n">
-        <v>5652.3326</v>
+        <v>3565.75736</v>
       </c>
       <c r="AC9" t="n">
-        <v>21.894816</v>
+        <v>75.454998</v>
       </c>
       <c r="AD9" t="n">
-        <v>1316.49283</v>
+        <v>2144.978265</v>
       </c>
       <c r="AE9" t="n">
-        <v>119012628.2427152</v>
+        <v>58110891.25980759</v>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
@@ -1837,12 +1841,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>REZUSDT</t>
+          <t>ZKUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Renzo</t>
+          <t>ZKsync</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1852,7 +1856,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_chased</t>
+          <t>entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1866,36 +1870,40 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>71.76000000000001</v>
+        <v>66.392</v>
       </c>
       <c r="I10" t="n">
-        <v>89.7</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N10" t="b">
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.003302794856571019</v>
+        <v>0.01959585256778836</v>
       </c>
       <c r="P10" t="n">
-        <v>0.003731</v>
+        <v>0.02087</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.96493309528604</v>
+        <v>6.50212807941859</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1903,43 +1911,43 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>0.002644</v>
+        <v>0.01778</v>
       </c>
       <c r="T10" t="n">
-        <v>19.94658721416878</v>
+        <v>9.266514745948117</v>
       </c>
       <c r="U10" t="n">
-        <v>0.003961589713142038</v>
+        <v>0.02141170513557672</v>
       </c>
       <c r="V10" t="n">
-        <v>0.004620384569713056</v>
+        <v>0.02322755770336508</v>
       </c>
       <c r="W10" t="n">
-        <v>0.005279179426284076</v>
+        <v>0.02504341027115345</v>
       </c>
       <c r="X10" t="n">
-        <v>1.000000000000001</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.999999999999999</v>
+        <v>2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.1338867318248707</v>
+        <v>0.04783544606554921</v>
       </c>
       <c r="AA10" t="n">
-        <v>12424.6138814</v>
+        <v>47274.4740612</v>
       </c>
       <c r="AB10" t="n">
-        <v>9307.115784449999</v>
+        <v>58380.6843272</v>
       </c>
       <c r="AC10" t="n">
-        <v>22.008812</v>
+        <v>22.622443</v>
       </c>
       <c r="AD10" t="n">
-        <v>159.976064</v>
+        <v>39.779511</v>
       </c>
       <c r="AE10" t="n">
-        <v>28868634.41804522</v>
+        <v>193921738.6876874</v>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
@@ -1954,12 +1962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FARTCOINUSDT</t>
+          <t>MUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fartcoin</t>
+          <t>MemeCore</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1969,24 +1977,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_chased</t>
+          <t>tradeability_marginal | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>breakout</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>fresh_breakout</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>69.968</v>
+        <v>66.03616599999999</v>
       </c>
       <c r="I11" t="n">
-        <v>87.45999999999999</v>
+        <v>66.03616599999999</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
@@ -2006,13 +2014,13 @@
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1675362954605856</v>
+        <v>1.56624</v>
       </c>
       <c r="P11" t="n">
-        <v>0.20213</v>
+        <v>1.74695</v>
       </c>
       <c r="Q11" t="n">
-        <v>20.64848362816576</v>
+        <v>11.5378230667075</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2020,19 +2028,19 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>0.13836</v>
+        <v>1.485268466728675</v>
       </c>
       <c r="T11" t="n">
-        <v>17.41491023206344</v>
+        <v>5.169803687259019</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1967125909211711</v>
+        <v>1.647211533271326</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2258888863817567</v>
+        <v>1.728183066542652</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2550651818423423</v>
+        <v>1.809154599813977</v>
       </c>
       <c r="X11" t="n">
         <v>1</v>
@@ -2041,22 +2049,22 @@
         <v>2</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.2422444691632769</v>
+        <v>0.1257796911536845</v>
       </c>
       <c r="AA11" t="n">
-        <v>12671.1958961</v>
+        <v>4020.179897</v>
       </c>
       <c r="AB11" t="n">
-        <v>7748.6464652</v>
+        <v>6949.0029706</v>
       </c>
       <c r="AC11" t="n">
-        <v>38.898461</v>
+        <v>22.15674</v>
       </c>
       <c r="AD11" t="n">
-        <v>82.370075</v>
+        <v>1051.641306</v>
       </c>
       <c r="AE11" t="n">
-        <v>203277202.3288137</v>
+        <v>2233919070.459943</v>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
@@ -2071,12 +2079,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ZECUSDT</t>
+          <t>BONKUSDT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Zcash</t>
+          <t>Bonk</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2086,7 +2094,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>effective_rr_insufficient | entry_chased</t>
+          <t>entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2100,15 +2108,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>68.792</v>
+        <v>65.72799999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>85.98999999999999</v>
+        <v>82.16</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>direct</t>
@@ -2123,13 +2135,13 @@
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>229.6644212431871</v>
+        <v>6.116580042993848e-06</v>
       </c>
       <c r="P12" t="n">
-        <v>265.96</v>
+        <v>6.426e-06</v>
       </c>
       <c r="Q12" t="n">
-        <v>15.80374468119303</v>
+        <v>5.058708540249923</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -2137,19 +2149,19 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>185</v>
+        <v>5.135e-06</v>
       </c>
       <c r="T12" t="n">
-        <v>19.44768850195251</v>
+        <v>16.04785739897551</v>
       </c>
       <c r="U12" t="n">
-        <v>274.3288424863741</v>
+        <v>7.098160085987695e-06</v>
       </c>
       <c r="V12" t="n">
-        <v>318.9932637295612</v>
+        <v>8.079740128981543e-06</v>
       </c>
       <c r="W12" t="n">
-        <v>363.6576849727483</v>
+        <v>9.061320171975392e-06</v>
       </c>
       <c r="X12" t="n">
         <v>1</v>
@@ -2158,22 +2170,22 @@
         <v>2</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.007522190461855652</v>
+        <v>0.1243008079552479</v>
       </c>
       <c r="AA12" t="n">
-        <v>109999.19126092</v>
+        <v>141446.879968649</v>
       </c>
       <c r="AB12" t="n">
-        <v>82242.11799442</v>
+        <v>104208.376136778</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.462161</v>
+        <v>6.21504</v>
       </c>
       <c r="AD12" t="n">
-        <v>17.708962</v>
+        <v>15.512563</v>
       </c>
       <c r="AE12" t="n">
-        <v>4426767598.352935</v>
+        <v>566117408.0313501</v>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
@@ -2188,12 +2200,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MEUSDT</t>
+          <t>RLCUSDT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Magic Eden</t>
+          <t>iExec RLC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2217,10 +2229,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>67.384</v>
+        <v>65.584</v>
       </c>
       <c r="I13" t="n">
-        <v>84.23</v>
+        <v>81.98</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -2244,13 +2256,13 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1190546835514273</v>
+        <v>0.4023141535192251</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1253</v>
+        <v>0.4497</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.245754524117441</v>
+        <v>11.77831952126698</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -2258,43 +2270,43 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>0.1106</v>
+        <v>0.3518</v>
       </c>
       <c r="T13" t="n">
-        <v>7.101512766421464</v>
+        <v>12.55589769272465</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1275093671028546</v>
+        <v>0.4528283070384502</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1359640506542819</v>
+        <v>0.5033424605576753</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1444187342057091</v>
+        <v>0.5538566140769005</v>
       </c>
       <c r="X13" t="n">
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>2</v>
+        <v>1.999999999999999</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.07984031936126865</v>
+        <v>0.2880248144455574</v>
       </c>
       <c r="AA13" t="n">
-        <v>16987.199246</v>
+        <v>6555.92775</v>
       </c>
       <c r="AB13" t="n">
-        <v>5346.393833</v>
+        <v>8224.385313999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>44.265473</v>
+        <v>35.660819</v>
       </c>
       <c r="AD13" t="n">
-        <v>1576.607302</v>
+        <v>236.555748</v>
       </c>
       <c r="AE13" t="n">
-        <v>59143891.08597557</v>
+        <v>39230827.60174326</v>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
@@ -2309,12 +2321,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BBUSDT</t>
+          <t>ACHUSDT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BounceBit</t>
+          <t>Alchemy Pay</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2324,7 +2336,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_late</t>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2338,10 +2350,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>66.91200000000001</v>
+        <v>63.152</v>
       </c>
       <c r="I14" t="n">
-        <v>83.64</v>
+        <v>78.94</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -2365,57 +2377,57 @@
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.02803792221883937</v>
+        <v>0.007042603236678154</v>
       </c>
       <c r="P14" t="n">
-        <v>0.02827</v>
+        <v>0.007514</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.8277281723989116</v>
+        <v>6.69350164250051</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>late</t>
+          <t>chased</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>0.0235</v>
+        <v>0.006221</v>
       </c>
       <c r="T14" t="n">
-        <v>16.18494474526444</v>
+        <v>11.66618662257178</v>
       </c>
       <c r="U14" t="n">
-        <v>0.03257584443767875</v>
+        <v>0.007864206473356308</v>
       </c>
       <c r="V14" t="n">
-        <v>0.03711376665651812</v>
+        <v>0.008685809710034463</v>
       </c>
       <c r="W14" t="n">
-        <v>0.04165168887535749</v>
+        <v>0.009507412946712618</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0.9999999999999989</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.000000000000001</v>
+        <v>2</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.1060632844263701</v>
+        <v>0.1998534408100645</v>
       </c>
       <c r="AA14" t="n">
-        <v>6045.2864785</v>
+        <v>17121.81179649</v>
       </c>
       <c r="AB14" t="n">
-        <v>5489.5224977</v>
+        <v>5001.72296197</v>
       </c>
       <c r="AC14" t="n">
-        <v>15.874753</v>
+        <v>67.692263</v>
       </c>
       <c r="AD14" t="n">
-        <v>179.834899</v>
+        <v>278.244895</v>
       </c>
       <c r="AE14" t="n">
-        <v>29509182.50367208</v>
+        <v>75299172.72841798</v>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
@@ -2430,12 +2442,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MUSDT</t>
+          <t>NEOUSDT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MemeCore</t>
+          <t>Neo</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2445,29 +2457,33 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>tradeability_marginal | btc_regime_caution | entry_chased</t>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>breakout</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>fresh_breakout</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>65.790415</v>
+        <v>62.24</v>
       </c>
       <c r="I15" t="n">
-        <v>65.790415</v>
+        <v>77.8</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>none</t>
@@ -2482,13 +2498,13 @@
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.56624</v>
+        <v>2.663747724979867</v>
       </c>
       <c r="P15" t="n">
-        <v>1.714</v>
+        <v>2.823</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.434058637245869</v>
+        <v>5.978504402902352</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -2496,19 +2512,19 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>1.485268466728675</v>
+        <v>2.419</v>
       </c>
       <c r="T15" t="n">
-        <v>5.169803687259019</v>
+        <v>9.188097006510514</v>
       </c>
       <c r="U15" t="n">
-        <v>1.647211533271326</v>
+        <v>2.908495449959734</v>
       </c>
       <c r="V15" t="n">
-        <v>1.728183066542652</v>
+        <v>3.153243174939601</v>
       </c>
       <c r="W15" t="n">
-        <v>1.809154599813977</v>
+        <v>3.397990899919468</v>
       </c>
       <c r="X15" t="n">
         <v>1</v>
@@ -2517,22 +2533,22 @@
         <v>2</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.1097585894853537</v>
+        <v>0.03539196602370872</v>
       </c>
       <c r="AA15" t="n">
-        <v>2760.4510547</v>
+        <v>16729.029661</v>
       </c>
       <c r="AB15" t="n">
-        <v>6746.1808777</v>
+        <v>13607.129249</v>
       </c>
       <c r="AC15" t="n">
-        <v>23.537474</v>
+        <v>13.294779</v>
       </c>
       <c r="AD15" t="n">
-        <v>1410.028214</v>
+        <v>78.45234000000001</v>
       </c>
       <c r="AE15" t="n">
-        <v>2186782198.947423</v>
+        <v>199202098.8102723</v>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
@@ -2547,12 +2563,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BONKUSDT</t>
+          <t>BANUSDT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bonk</t>
+          <t>Comedian</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2562,54 +2578,50 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>65.72799999999999</v>
+        <v>61.2</v>
       </c>
       <c r="I16" t="n">
-        <v>82.16</v>
+        <v>68</v>
       </c>
       <c r="J16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N16" t="b">
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>6.116580042993848e-06</v>
+        <v>0.1355225963721603</v>
       </c>
       <c r="P16" t="n">
-        <v>6.406e-06</v>
+        <v>0.16765</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.731728432748361</v>
+        <v>23.70630764748205</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -2617,19 +2629,19 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>5.135e-06</v>
+        <v>0.1257953400014318</v>
       </c>
       <c r="T16" t="n">
-        <v>16.04785739897551</v>
+        <v>7.177590033780329</v>
       </c>
       <c r="U16" t="n">
-        <v>7.098160085987695e-06</v>
+        <v>0.1452498527428888</v>
       </c>
       <c r="V16" t="n">
-        <v>8.079740128981543e-06</v>
+        <v>0.1549771091136174</v>
       </c>
       <c r="W16" t="n">
-        <v>9.061320171975392e-06</v>
+        <v>0.1647043654843459</v>
       </c>
       <c r="X16" t="n">
         <v>1</v>
@@ -2638,22 +2650,22 @@
         <v>2</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.1248829222603771</v>
+        <v>0.09524376450978837</v>
       </c>
       <c r="AA16" t="n">
-        <v>204220.24221031</v>
+        <v>242.8176689</v>
       </c>
       <c r="AB16" t="n">
-        <v>116491.017283149</v>
+        <v>38.43508050000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.707638</v>
+        <v>606.417869</v>
       </c>
       <c r="AD16" t="n">
-        <v>9.176501999999999</v>
+        <v>1961.302199</v>
       </c>
       <c r="AE16" t="n">
-        <v>563792403.1819856</v>
+        <v>167369038.0239686</v>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
@@ -2668,12 +2680,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ALGOUSDT</t>
+          <t>DEXEUSDT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algorand</t>
+          <t>DeXe</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2683,24 +2695,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>effective_rr_insufficient | entry_chased</t>
+          <t>tradeability_marginal | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>64.608</v>
+        <v>61.2</v>
       </c>
       <c r="I17" t="n">
-        <v>80.76000000000001</v>
+        <v>68</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
@@ -2708,25 +2720,25 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N17" t="b">
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0.08960487930633863</v>
+        <v>5.124723018133185</v>
       </c>
       <c r="P17" t="n">
-        <v>0.09432</v>
+        <v>5.423</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.26212493132372</v>
+        <v>5.820353232972786</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -2734,19 +2746,19 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>0.0806</v>
+        <v>4.764082143488518</v>
       </c>
       <c r="T17" t="n">
-        <v>10.0495412482539</v>
+        <v>7.037275446274556</v>
       </c>
       <c r="U17" t="n">
-        <v>0.09860975861267726</v>
+        <v>5.485363892777852</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1076146379190159</v>
+        <v>5.846004767422519</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1166195172253545</v>
+        <v>6.206645642067186</v>
       </c>
       <c r="X17" t="n">
         <v>1</v>
@@ -2755,22 +2767,22 @@
         <v>2</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.06361997667266527</v>
+        <v>0.01842468908337787</v>
       </c>
       <c r="AA17" t="n">
-        <v>92247.7703564</v>
+        <v>1576.27559</v>
       </c>
       <c r="AB17" t="n">
-        <v>94093.4121284</v>
+        <v>2078.82757</v>
       </c>
       <c r="AC17" t="n">
-        <v>14.180392</v>
+        <v>141.258695</v>
       </c>
       <c r="AD17" t="n">
-        <v>19.449168</v>
+        <v>528.480269</v>
       </c>
       <c r="AE17" t="n">
-        <v>839458951.4464691</v>
+        <v>453479867.3362362</v>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
@@ -2785,22 +2797,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>XRPUSDT</t>
+          <t>LAYERUSDT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>Solayer</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NO_TRADE</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2814,36 +2826,40 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>76.36</v>
+        <v>61.168</v>
       </c>
       <c r="I18" t="n">
-        <v>95.45</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.414756719200329</v>
+        <v>0.08553809548486238</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5245</v>
+        <v>0.08867999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.757042557938987</v>
+        <v>3.673105529563303</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -2851,43 +2867,43 @@
         </is>
       </c>
       <c r="S18" t="n">
-        <v>1.12</v>
+        <v>0.07028</v>
       </c>
       <c r="T18" t="n">
-        <v>20.83444561174701</v>
+        <v>17.83777789109485</v>
       </c>
       <c r="U18" t="n">
-        <v>1.709513438400658</v>
+        <v>0.1007961909697248</v>
       </c>
       <c r="V18" t="n">
-        <v>2.004270157600986</v>
+        <v>0.1160542864545872</v>
       </c>
       <c r="W18" t="n">
-        <v>2.299026876801316</v>
+        <v>0.1313123819394496</v>
       </c>
       <c r="X18" t="n">
         <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.999999999999999</v>
+        <v>2</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.01966890673661295</v>
+        <v>0.1465036344170903</v>
       </c>
       <c r="AA18" t="n">
-        <v>793830.259769</v>
+        <v>5267.2081632</v>
       </c>
       <c r="AB18" t="n">
-        <v>907173.516524</v>
+        <v>9429.638013100001</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.475105</v>
+        <v>38.684651</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.792347</v>
+        <v>135.465016</v>
       </c>
       <c r="AE18" t="n">
-        <v>93596020174.53885</v>
+        <v>35323932.13587327</v>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
@@ -2902,12 +2918,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HYPEUSDT</t>
+          <t>IMXUSDT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hyperliquid</t>
+          <t>Immutable</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2917,24 +2933,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>breakout</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>confirmed_breakout</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>74.601945</v>
+        <v>73.968</v>
       </c>
       <c r="I19" t="n">
-        <v>74.601945</v>
+        <v>92.45999999999999</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
@@ -2942,25 +2958,25 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N19" t="b">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>38.86</v>
+        <v>0.1650630349830551</v>
       </c>
       <c r="P19" t="n">
-        <v>40.65</v>
+        <v>0.1783</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.606278950077192</v>
+        <v>8.019339410731053</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -2968,19 +2984,19 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>34.11745653141787</v>
+        <v>0.1288</v>
       </c>
       <c r="T19" t="n">
-        <v>12.20417773695864</v>
+        <v>21.96920405999909</v>
       </c>
       <c r="U19" t="n">
-        <v>43.60254346858213</v>
+        <v>0.2013260699661101</v>
       </c>
       <c r="V19" t="n">
-        <v>48.34508693716425</v>
+        <v>0.2375891049491652</v>
       </c>
       <c r="W19" t="n">
-        <v>53.08763040574638</v>
+        <v>0.2738521399322202</v>
       </c>
       <c r="X19" t="n">
         <v>1</v>
@@ -2989,22 +3005,22 @@
         <v>2</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.04917629702484172</v>
+        <v>0.056038105912014</v>
       </c>
       <c r="AA19" t="n">
-        <v>76931.7404</v>
+        <v>12869.873846</v>
       </c>
       <c r="AB19" t="n">
-        <v>56724.93960000001</v>
+        <v>11686.979658</v>
       </c>
       <c r="AC19" t="n">
-        <v>12.712685</v>
+        <v>27.432788</v>
       </c>
       <c r="AD19" t="n">
-        <v>23.708315</v>
+        <v>204.391727</v>
       </c>
       <c r="AE19" t="n">
-        <v>10497688985.53881</v>
+        <v>354967033.4957088</v>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
@@ -3019,12 +3035,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ASTERUSDT</t>
+          <t>HYPEUSDT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Hyperliquid</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3034,24 +3050,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | entry_chased</t>
+          <t>risk_reward_unattractive | btc_regime_caution | entry_late</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>breakout</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>confirmed_breakout</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>69.16</v>
+        <v>69.841424</v>
       </c>
       <c r="I20" t="n">
-        <v>86.45</v>
+        <v>69.841424</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
@@ -3071,57 +3087,57 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7055770637341362</v>
+        <v>38.86</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7288</v>
+        <v>39.72</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.291339452413711</v>
+        <v>2.213072568193519</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>chased</t>
+          <t>late</t>
         </is>
       </c>
       <c r="S20" t="n">
-        <v>0.404</v>
+        <v>34.11745653141787</v>
       </c>
       <c r="T20" t="n">
-        <v>42.74190293801436</v>
+        <v>12.20417773695864</v>
       </c>
       <c r="U20" t="n">
-        <v>1.007154127468272</v>
+        <v>43.60254346858213</v>
       </c>
       <c r="V20" t="n">
-        <v>1.308731191202408</v>
+        <v>48.34508693716425</v>
       </c>
       <c r="W20" t="n">
-        <v>1.610308254936545</v>
+        <v>53.08763040574638</v>
       </c>
       <c r="X20" t="n">
-        <v>0.9999999999999997</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
         <v>2</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.02746875429198984</v>
+        <v>0.0251667295835035</v>
       </c>
       <c r="AA20" t="n">
-        <v>272294.810961</v>
+        <v>77037.26669999999</v>
       </c>
       <c r="AB20" t="n">
-        <v>233724.321077</v>
+        <v>81424.85770000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>10.735823</v>
+        <v>4.390817</v>
       </c>
       <c r="AD20" t="n">
-        <v>12.98457</v>
+        <v>11.910691</v>
       </c>
       <c r="AE20" t="n">
-        <v>1803979844.919093</v>
+        <v>10207919597.19811</v>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
@@ -3191,10 +3207,10 @@
         <v>9.105111163632445</v>
       </c>
       <c r="P21" t="n">
-        <v>9.762</v>
+        <v>9.757</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.214506495992001</v>
+        <v>7.15959228451073</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -3223,22 +3239,22 @@
         <v>2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.03072353935173448</v>
+        <v>0.01024222870896139</v>
       </c>
       <c r="AA21" t="n">
-        <v>898907.95284</v>
+        <v>926758.89771</v>
       </c>
       <c r="AB21" t="n">
-        <v>933745.9345900001</v>
+        <v>945394.59074</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.114999</v>
+        <v>2.404793</v>
       </c>
       <c r="AD21" t="n">
-        <v>6.27128</v>
+        <v>5.562133</v>
       </c>
       <c r="AE21" t="n">
-        <v>6921467270.492787</v>
+        <v>6917834477.289282</v>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
@@ -3259,7 +3275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG5"/>
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3485,7 +3501,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>entry_chased</t>
+          <t>entry_late</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3525,14 +3541,14 @@
         <v>3.570573042426071e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>3.802e-06</v>
+        <v>3.633e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.481507444997758</v>
+        <v>1.748373631687761</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>chased</t>
+          <t>late</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -3557,22 +3573,22 @@
         <v>2.000000000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.07883326763894954</v>
+        <v>0.02752167331772813</v>
       </c>
       <c r="AA2" t="n">
-        <v>281035.212427225</v>
+        <v>831628.6260935001</v>
       </c>
       <c r="AB2" t="n">
-        <v>303972.512402603</v>
+        <v>568280.167103815</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.822627000000001</v>
+        <v>9.201302</v>
       </c>
       <c r="AD2" t="n">
-        <v>15.65917</v>
+        <v>14.914928</v>
       </c>
       <c r="AE2" t="n">
-        <v>1574788786.790929</v>
+        <v>1503762547.232597</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -3581,359 +3597,8 @@
       </c>
       <c r="AG2" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>SUIUSDT</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Sui</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ENTER</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>entry_chased</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>reversal</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>reversal_base_reclaim</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>65.864</v>
-      </c>
-      <c r="I3" t="n">
-        <v>82.33</v>
-      </c>
-      <c r="J3" t="b">
-        <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>DIRECT_OK</t>
-        </is>
-      </c>
-      <c r="N3" t="b">
-        <v>1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.9740674814932353</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.029</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>5.639498243238106</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>chased</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>0.789</v>
-      </c>
-      <c r="T3" t="n">
-        <v>18.99945178433929</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.15913496298647</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.344202444479706</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.529269925972941</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.9999999999999994</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.009708266588999464</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>313244.558082</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>346435.702239</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.700078</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>4.358873</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>4021498012.456191</v>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>RISK_OFF</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>XLMUSDT</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Stellar</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ENTER</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>entry_chased</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>reversal</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>reversal_base_reclaim</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>64.44799999999999</v>
-      </c>
-      <c r="I4" t="n">
-        <v>80.56</v>
-      </c>
-      <c r="J4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>DIRECT_OK</t>
-        </is>
-      </c>
-      <c r="N4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.1615448108821275</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.1739</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>7.648149792250214</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>chased</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>0.1362</v>
-      </c>
-      <c r="T4" t="n">
-        <v>15.6890281673118</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.1868896217642551</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.2122344326463827</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.2375792435285102</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.05752085130859303</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>195551.569347</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>260127.512412</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.876043</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>8.243309999999999</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>5748011796.422249</v>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>RISK_OFF</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>LTCUSDT</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Litecoin</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ENTER</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>entry_chased</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>reversal</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>reversal_base_reclaim</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>64.06399999999999</v>
-      </c>
-      <c r="I5" t="n">
-        <v>80.08</v>
-      </c>
-      <c r="J5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>DIRECT_OK</t>
-        </is>
-      </c>
-      <c r="N5" t="b">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>55.19368745876001</v>
-      </c>
-      <c r="P5" t="n">
-        <v>57.86</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4.83082878496246</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>chased</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>45</v>
-      </c>
-      <c r="T5" t="n">
-        <v>18.46893717035412</v>
-      </c>
-      <c r="U5" t="n">
-        <v>65.38737491752002</v>
-      </c>
-      <c r="V5" t="n">
-        <v>75.58106237628003</v>
-      </c>
-      <c r="W5" t="n">
-        <v>85.77474983504004</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.01727861771059199</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>421843.257056</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>254673.128187</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.95594</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.323295</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>4453487185.845181</v>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>RISK_OFF</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AG5"/>
+  <autoFilter ref="A1:AG2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3944,7 +3609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG13"/>
+  <dimension ref="A1:AG17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4151,16 +3816,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CROUSDT</t>
+          <t>TRXUSDT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cronos</t>
+          <t>TRON</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -4170,7 +3835,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_chased</t>
+          <t>effective_rr_insufficient | entry_chased</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -4184,10 +3849,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>76.65600000000001</v>
+        <v>74.752</v>
       </c>
       <c r="I2" t="n">
-        <v>95.81999999999999</v>
+        <v>93.44</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -4195,25 +3860,25 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N2" t="b">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07706222520171957</v>
+        <v>0.2893153896519431</v>
       </c>
       <c r="P2" t="n">
-        <v>0.07964</v>
+        <v>0.3042</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.345056273073865</v>
+        <v>5.144769646012826</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -4221,19 +3886,19 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>0.06811</v>
+        <v>0.268</v>
       </c>
       <c r="T2" t="n">
-        <v>11.61687866952459</v>
+        <v>7.367527070573851</v>
       </c>
       <c r="U2" t="n">
-        <v>0.08601445040343914</v>
+        <v>0.3106307793038863</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0949666756051587</v>
+        <v>0.3319461689558294</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1039189008068783</v>
+        <v>0.3532615586077725</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
@@ -4242,22 +3907,22 @@
         <v>2</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.08790104853393685</v>
+        <v>0.03287851389118675</v>
       </c>
       <c r="AA2" t="n">
-        <v>8513.6971428</v>
+        <v>1529175.661605</v>
       </c>
       <c r="AB2" t="n">
-        <v>7202.0159494</v>
+        <v>967099.6149340001</v>
       </c>
       <c r="AC2" t="n">
-        <v>32.753152</v>
+        <v>1.643926</v>
       </c>
       <c r="AD2" t="n">
-        <v>365.165237</v>
+        <v>1.643926</v>
       </c>
       <c r="AE2" t="n">
-        <v>3285511403.793965</v>
+        <v>28807874085.95885</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -4268,16 +3933,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KASUSDT</t>
+          <t>SUSDT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kaspa</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4301,10 +3966,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>74.44</v>
+        <v>73.032</v>
       </c>
       <c r="I3" t="n">
-        <v>93.05</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -4324,13 +3989,13 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03091180535852996</v>
+        <v>0.04320432927693411</v>
       </c>
       <c r="P3" t="n">
-        <v>0.035</v>
+        <v>0.04854</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.22535061945815</v>
+        <v>12.34985199947196</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -4338,43 +4003,43 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0.025188</v>
+        <v>0.03667</v>
       </c>
       <c r="T3" t="n">
-        <v>18.51656767420252</v>
+        <v>15.12424654263213</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03663561071705992</v>
+        <v>0.04973865855386821</v>
       </c>
       <c r="V3" t="n">
-        <v>0.04235941607558988</v>
+        <v>0.05627298783080232</v>
       </c>
       <c r="W3" t="n">
-        <v>0.04808322143411985</v>
+        <v>0.06280731710773643</v>
       </c>
       <c r="X3" t="n">
-        <v>1.000000000000001</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.999999999999999</v>
+        <v>2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1002822228271</v>
+        <v>0.02058672156458286</v>
       </c>
       <c r="AA3" t="n">
-        <v>42900.87676025</v>
+        <v>19553.5759032</v>
       </c>
       <c r="AB3" t="n">
-        <v>11873.70124821</v>
+        <v>13143.0154511</v>
       </c>
       <c r="AC3" t="n">
-        <v>11.450943</v>
+        <v>15.154426</v>
       </c>
       <c r="AD3" t="n">
-        <v>66.481675</v>
+        <v>354.823323</v>
       </c>
       <c r="AE3" t="n">
-        <v>957875665.1243513</v>
+        <v>139858424.4330002</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
@@ -4385,16 +4050,16 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SUSDT</t>
+          <t>ZENUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>Horizen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4418,10 +4083,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>73.032</v>
+        <v>72.104</v>
       </c>
       <c r="I4" t="n">
-        <v>91.29000000000001</v>
+        <v>90.13</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -4441,13 +4106,13 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04320432927693411</v>
+        <v>5.764233529855139</v>
       </c>
       <c r="P4" t="n">
-        <v>0.04822</v>
+        <v>6.619</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.60918548443628</v>
+        <v>14.82879667726338</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -4455,19 +4120,19 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0.03667</v>
+        <v>4.94</v>
       </c>
       <c r="T4" t="n">
-        <v>15.12424654263213</v>
+        <v>14.29910022878363</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04973865855386821</v>
+        <v>6.588467059710278</v>
       </c>
       <c r="V4" t="n">
-        <v>0.05627298783080232</v>
+        <v>7.412700589565417</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06280731710773643</v>
+        <v>8.236934119420557</v>
       </c>
       <c r="X4" t="n">
         <v>1</v>
@@ -4476,22 +4141,22 @@
         <v>2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02074904035688985</v>
+        <v>0.03019323671497252</v>
       </c>
       <c r="AA4" t="n">
-        <v>17296.7617039</v>
+        <v>7487.28291</v>
       </c>
       <c r="AB4" t="n">
-        <v>25089.7056129</v>
+        <v>7368.29412</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.178</v>
+        <v>18.150932</v>
       </c>
       <c r="AD4" t="n">
-        <v>24.494745</v>
+        <v>410.330327</v>
       </c>
       <c r="AE4" t="n">
-        <v>139100289.1268733</v>
+        <v>118483517.806406</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
@@ -4502,16 +4167,16 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ZENUSDT</t>
+          <t>REZUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Horizen</t>
+          <t>Renzo</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4535,10 +4200,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>72.104</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>90.13</v>
+        <v>89.7</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -4558,13 +4223,13 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>5.764233529855139</v>
+        <v>0.003302794856571019</v>
       </c>
       <c r="P5" t="n">
-        <v>6.623</v>
+        <v>0.003496</v>
       </c>
       <c r="Q5" t="n">
-        <v>14.89819011837368</v>
+        <v>5.849747011825235</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -4572,43 +4237,43 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>4.94</v>
+        <v>0.002644</v>
       </c>
       <c r="T5" t="n">
-        <v>14.29910022878363</v>
+        <v>19.94658721416878</v>
       </c>
       <c r="U5" t="n">
-        <v>6.588467059710278</v>
+        <v>0.003961589713142038</v>
       </c>
       <c r="V5" t="n">
-        <v>7.412700589565417</v>
+        <v>0.004620384569713056</v>
       </c>
       <c r="W5" t="n">
-        <v>8.236934119420557</v>
+        <v>0.005279179426284076</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="Y5" t="n">
-        <v>2</v>
+        <v>1.999999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0453137980515084</v>
+        <v>0.171624713958808</v>
       </c>
       <c r="AA5" t="n">
-        <v>6939.51449</v>
+        <v>15379.33683327</v>
       </c>
       <c r="AB5" t="n">
-        <v>5652.3326</v>
+        <v>10728.90403699</v>
       </c>
       <c r="AC5" t="n">
-        <v>21.894816</v>
+        <v>20.545616</v>
       </c>
       <c r="AD5" t="n">
-        <v>1316.49283</v>
+        <v>92.307366</v>
       </c>
       <c r="AE5" t="n">
-        <v>119012628.2427152</v>
+        <v>27258722.09736478</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
@@ -4619,16 +4284,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>REZUSDT</t>
+          <t>KASUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Renzo</t>
+          <t>Kaspa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4652,10 +4317,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>71.76000000000001</v>
+        <v>70.328</v>
       </c>
       <c r="I6" t="n">
-        <v>89.7</v>
+        <v>87.91</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
@@ -4675,13 +4340,13 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.003302794856571019</v>
+        <v>0.03091180535852996</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003731</v>
+        <v>0.035605</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.96493309528604</v>
+        <v>15.18253168016592</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -4689,19 +4354,19 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>0.002644</v>
+        <v>0.025188</v>
       </c>
       <c r="T6" t="n">
-        <v>19.94658721416878</v>
+        <v>18.51656767420252</v>
       </c>
       <c r="U6" t="n">
-        <v>0.003961589713142038</v>
+        <v>0.03663561071705992</v>
       </c>
       <c r="V6" t="n">
-        <v>0.004620384569713056</v>
+        <v>0.04235941607558988</v>
       </c>
       <c r="W6" t="n">
-        <v>0.005279179426284076</v>
+        <v>0.04808322143411985</v>
       </c>
       <c r="X6" t="n">
         <v>1.000000000000001</v>
@@ -4710,22 +4375,22 @@
         <v>1.999999999999999</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.1338867318248707</v>
+        <v>0.1289382217737537</v>
       </c>
       <c r="AA6" t="n">
-        <v>12424.6138814</v>
+        <v>55967.13071129</v>
       </c>
       <c r="AB6" t="n">
-        <v>9307.115784449999</v>
+        <v>20457.86793545</v>
       </c>
       <c r="AC6" t="n">
-        <v>22.008812</v>
+        <v>26.682585</v>
       </c>
       <c r="AD6" t="n">
-        <v>159.976064</v>
+        <v>51.172304</v>
       </c>
       <c r="AE6" t="n">
-        <v>28868634.41804522</v>
+        <v>975806733.049776</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
@@ -4736,16 +4401,16 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FARTCOINUSDT</t>
+          <t>ZECUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fartcoin</t>
+          <t>Zcash</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4755,7 +4420,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_chased</t>
+          <t>effective_rr_insufficient | entry_chased</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4769,10 +4434,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>69.968</v>
+        <v>68.792</v>
       </c>
       <c r="I7" t="n">
-        <v>87.45999999999999</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
@@ -4780,25 +4445,25 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N7" t="b">
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1675362954605856</v>
+        <v>229.6644212431871</v>
       </c>
       <c r="P7" t="n">
-        <v>0.20213</v>
+        <v>268.65</v>
       </c>
       <c r="Q7" t="n">
-        <v>20.64848362816576</v>
+        <v>16.97501883216464</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -4806,19 +4471,19 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>0.13836</v>
+        <v>185</v>
       </c>
       <c r="T7" t="n">
-        <v>17.41491023206344</v>
+        <v>19.44768850195251</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1967125909211711</v>
+        <v>274.3288424863741</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2258888863817567</v>
+        <v>318.9932637295612</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2550651818423423</v>
+        <v>363.6576849727483</v>
       </c>
       <c r="X7" t="n">
         <v>1</v>
@@ -4827,22 +4492,22 @@
         <v>2</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2422444691632769</v>
+        <v>0.003721691881125777</v>
       </c>
       <c r="AA7" t="n">
-        <v>12671.1958961</v>
+        <v>117906.88669995</v>
       </c>
       <c r="AB7" t="n">
-        <v>7748.6464652</v>
+        <v>71126.95808521</v>
       </c>
       <c r="AC7" t="n">
-        <v>38.898461</v>
+        <v>7.961808</v>
       </c>
       <c r="AD7" t="n">
-        <v>82.370075</v>
+        <v>11.554508</v>
       </c>
       <c r="AE7" t="n">
-        <v>203277202.3288137</v>
+        <v>4445895174.543806</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
@@ -4853,16 +4518,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ZECUSDT</t>
+          <t>MEUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Zcash</t>
+          <t>Magic Eden</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4872,7 +4537,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>effective_rr_insufficient | entry_chased</t>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4886,36 +4551,40 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>68.792</v>
+        <v>67.384</v>
       </c>
       <c r="I8" t="n">
-        <v>85.98999999999999</v>
+        <v>84.23</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N8" t="b">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>229.6644212431871</v>
+        <v>0.1190546835514273</v>
       </c>
       <c r="P8" t="n">
-        <v>265.96</v>
+        <v>0.1228</v>
       </c>
       <c r="Q8" t="n">
-        <v>15.80374468119303</v>
+        <v>3.145879134570029</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -4923,19 +4592,19 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>185</v>
+        <v>0.1106</v>
       </c>
       <c r="T8" t="n">
-        <v>19.44768850195251</v>
+        <v>7.101512766421464</v>
       </c>
       <c r="U8" t="n">
-        <v>274.3288424863741</v>
+        <v>0.1275093671028546</v>
       </c>
       <c r="V8" t="n">
-        <v>318.9932637295612</v>
+        <v>0.1359640506542819</v>
       </c>
       <c r="W8" t="n">
-        <v>363.6576849727483</v>
+        <v>0.1444187342057091</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
@@ -4944,22 +4613,22 @@
         <v>2</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.007522190461855652</v>
+        <v>0.08146639511201863</v>
       </c>
       <c r="AA8" t="n">
-        <v>109999.19126092</v>
+        <v>12477.055833</v>
       </c>
       <c r="AB8" t="n">
-        <v>82242.11799442</v>
+        <v>3565.75736</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.462161</v>
+        <v>75.454998</v>
       </c>
       <c r="AD8" t="n">
-        <v>17.708962</v>
+        <v>2144.978265</v>
       </c>
       <c r="AE8" t="n">
-        <v>4426767598.352935</v>
+        <v>58110891.25980759</v>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
@@ -4970,16 +4639,16 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MEUSDT</t>
+          <t>ZKUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Magic Eden</t>
+          <t>ZKsync</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4989,7 +4658,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5003,10 +4672,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>67.384</v>
+        <v>66.392</v>
       </c>
       <c r="I9" t="n">
-        <v>84.23</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -5018,25 +4687,25 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N9" t="b">
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1190546835514273</v>
+        <v>0.01959585256778836</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1253</v>
+        <v>0.02087</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.245754524117441</v>
+        <v>6.50212807941859</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -5044,19 +4713,19 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>0.1106</v>
+        <v>0.01778</v>
       </c>
       <c r="T9" t="n">
-        <v>7.101512766421464</v>
+        <v>9.266514745948117</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1275093671028546</v>
+        <v>0.02141170513557672</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1359640506542819</v>
+        <v>0.02322755770336508</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1444187342057091</v>
+        <v>0.02504341027115345</v>
       </c>
       <c r="X9" t="n">
         <v>1</v>
@@ -5065,22 +4734,22 @@
         <v>2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.07984031936126865</v>
+        <v>0.04783544606554921</v>
       </c>
       <c r="AA9" t="n">
-        <v>16987.199246</v>
+        <v>47274.4740612</v>
       </c>
       <c r="AB9" t="n">
-        <v>5346.393833</v>
+        <v>58380.6843272</v>
       </c>
       <c r="AC9" t="n">
-        <v>44.265473</v>
+        <v>22.622443</v>
       </c>
       <c r="AD9" t="n">
-        <v>1576.607302</v>
+        <v>39.779511</v>
       </c>
       <c r="AE9" t="n">
-        <v>59143891.08597557</v>
+        <v>193921738.6876874</v>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
@@ -5091,16 +4760,16 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BBUSDT</t>
+          <t>MUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BounceBit</t>
+          <t>MemeCore</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5110,33 +4779,29 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_late</t>
+          <t>tradeability_marginal | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>breakout</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>fresh_breakout</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>66.91200000000001</v>
+        <v>66.03616599999999</v>
       </c>
       <c r="I10" t="n">
-        <v>83.64</v>
+        <v>66.03616599999999</v>
       </c>
       <c r="J10" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>none</t>
@@ -5151,57 +4816,57 @@
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02803792221883937</v>
+        <v>1.56624</v>
       </c>
       <c r="P10" t="n">
-        <v>0.02827</v>
+        <v>1.74695</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.8277281723989116</v>
+        <v>11.5378230667075</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>late</t>
+          <t>chased</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>0.0235</v>
+        <v>1.485268466728675</v>
       </c>
       <c r="T10" t="n">
-        <v>16.18494474526444</v>
+        <v>5.169803687259019</v>
       </c>
       <c r="U10" t="n">
-        <v>0.03257584443767875</v>
+        <v>1.647211533271326</v>
       </c>
       <c r="V10" t="n">
-        <v>0.03711376665651812</v>
+        <v>1.728183066542652</v>
       </c>
       <c r="W10" t="n">
-        <v>0.04165168887535749</v>
+        <v>1.809154599813977</v>
       </c>
       <c r="X10" t="n">
         <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.000000000000001</v>
+        <v>2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.1060632844263701</v>
+        <v>0.1257796911536845</v>
       </c>
       <c r="AA10" t="n">
-        <v>6045.2864785</v>
+        <v>4020.179897</v>
       </c>
       <c r="AB10" t="n">
-        <v>5489.5224977</v>
+        <v>6949.0029706</v>
       </c>
       <c r="AC10" t="n">
-        <v>15.874753</v>
+        <v>22.15674</v>
       </c>
       <c r="AD10" t="n">
-        <v>179.834899</v>
+        <v>1051.641306</v>
       </c>
       <c r="AE10" t="n">
-        <v>29509182.50367208</v>
+        <v>2233919070.459943</v>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
@@ -5212,16 +4877,16 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MUSDT</t>
+          <t>BONKUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MemeCore</t>
+          <t>Bonk</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5231,50 +4896,54 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>tradeability_marginal | btc_regime_caution | entry_chased</t>
+          <t>entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>breakout</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>fresh_breakout</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>65.790415</v>
+        <v>65.72799999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>65.790415</v>
+        <v>82.16</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N11" t="b">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.56624</v>
+        <v>6.116580042993848e-06</v>
       </c>
       <c r="P11" t="n">
-        <v>1.714</v>
+        <v>6.426e-06</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.434058637245869</v>
+        <v>5.058708540249923</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -5282,19 +4951,19 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>1.485268466728675</v>
+        <v>5.135e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>5.169803687259019</v>
+        <v>16.04785739897551</v>
       </c>
       <c r="U11" t="n">
-        <v>1.647211533271326</v>
+        <v>7.098160085987695e-06</v>
       </c>
       <c r="V11" t="n">
-        <v>1.728183066542652</v>
+        <v>8.079740128981543e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>1.809154599813977</v>
+        <v>9.061320171975392e-06</v>
       </c>
       <c r="X11" t="n">
         <v>1</v>
@@ -5303,22 +4972,22 @@
         <v>2</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.1097585894853537</v>
+        <v>0.1243008079552479</v>
       </c>
       <c r="AA11" t="n">
-        <v>2760.4510547</v>
+        <v>141446.879968649</v>
       </c>
       <c r="AB11" t="n">
-        <v>6746.1808777</v>
+        <v>104208.376136778</v>
       </c>
       <c r="AC11" t="n">
-        <v>23.537474</v>
+        <v>6.21504</v>
       </c>
       <c r="AD11" t="n">
-        <v>1410.028214</v>
+        <v>15.512563</v>
       </c>
       <c r="AE11" t="n">
-        <v>2186782198.947423</v>
+        <v>566117408.0313501</v>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
@@ -5329,16 +4998,16 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BONKUSDT</t>
+          <t>RLCUSDT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bonk</t>
+          <t>iExec RLC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5348,7 +5017,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -5362,10 +5031,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>65.72799999999999</v>
+        <v>65.584</v>
       </c>
       <c r="I12" t="n">
-        <v>82.16</v>
+        <v>81.98</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -5377,25 +5046,25 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N12" t="b">
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>6.116580042993848e-06</v>
+        <v>0.4023141535192251</v>
       </c>
       <c r="P12" t="n">
-        <v>6.406e-06</v>
+        <v>0.4497</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.731728432748361</v>
+        <v>11.77831952126698</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -5403,43 +5072,43 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>5.135e-06</v>
+        <v>0.3518</v>
       </c>
       <c r="T12" t="n">
-        <v>16.04785739897551</v>
+        <v>12.55589769272465</v>
       </c>
       <c r="U12" t="n">
-        <v>7.098160085987695e-06</v>
+        <v>0.4528283070384502</v>
       </c>
       <c r="V12" t="n">
-        <v>8.079740128981543e-06</v>
+        <v>0.5033424605576753</v>
       </c>
       <c r="W12" t="n">
-        <v>9.061320171975392e-06</v>
+        <v>0.5538566140769005</v>
       </c>
       <c r="X12" t="n">
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>2</v>
+        <v>1.999999999999999</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.1248829222603771</v>
+        <v>0.2880248144455574</v>
       </c>
       <c r="AA12" t="n">
-        <v>204220.24221031</v>
+        <v>6555.92775</v>
       </c>
       <c r="AB12" t="n">
-        <v>116491.017283149</v>
+        <v>8224.385313999999</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.707638</v>
+        <v>35.660819</v>
       </c>
       <c r="AD12" t="n">
-        <v>9.176501999999999</v>
+        <v>236.555748</v>
       </c>
       <c r="AE12" t="n">
-        <v>563792403.1819856</v>
+        <v>39230827.60174326</v>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
@@ -5450,16 +5119,16 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ALGOUSDT</t>
+          <t>ACHUSDT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algorand</t>
+          <t>Alchemy Pay</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5469,7 +5138,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>effective_rr_insufficient | entry_chased</t>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -5483,36 +5152,40 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>64.608</v>
+        <v>63.152</v>
       </c>
       <c r="I13" t="n">
-        <v>80.76000000000001</v>
+        <v>78.94</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N13" t="b">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.08960487930633863</v>
+        <v>0.007042603236678154</v>
       </c>
       <c r="P13" t="n">
-        <v>0.09432</v>
+        <v>0.007514</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.26212493132372</v>
+        <v>6.69350164250051</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -5520,43 +5193,43 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>0.0806</v>
+        <v>0.006221</v>
       </c>
       <c r="T13" t="n">
-        <v>10.0495412482539</v>
+        <v>11.66618662257178</v>
       </c>
       <c r="U13" t="n">
-        <v>0.09860975861267726</v>
+        <v>0.007864206473356308</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1076146379190159</v>
+        <v>0.008685809710034463</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1166195172253545</v>
+        <v>0.009507412946712618</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>0.9999999999999989</v>
       </c>
       <c r="Y13" t="n">
         <v>2</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.06361997667266527</v>
+        <v>0.1998534408100645</v>
       </c>
       <c r="AA13" t="n">
-        <v>92247.7703564</v>
+        <v>17121.81179649</v>
       </c>
       <c r="AB13" t="n">
-        <v>94093.4121284</v>
+        <v>5001.72296197</v>
       </c>
       <c r="AC13" t="n">
-        <v>14.180392</v>
+        <v>67.692263</v>
       </c>
       <c r="AD13" t="n">
-        <v>19.449168</v>
+        <v>278.244895</v>
       </c>
       <c r="AE13" t="n">
-        <v>839458951.4464691</v>
+        <v>75299172.72841798</v>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
@@ -5565,8 +5238,484 @@
       </c>
       <c r="AG13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NEOUSDT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Neo</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>reversal</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>reversal_base_reclaim</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>62.24</v>
+      </c>
+      <c r="I14" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>MARGINAL</t>
+        </is>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.663747724979867</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.823</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5.978504402902352</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>chased</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>2.419</v>
+      </c>
+      <c r="T14" t="n">
+        <v>9.188097006510514</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.908495449959734</v>
+      </c>
+      <c r="V14" t="n">
+        <v>3.153243174939601</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.397990899919468</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.03539196602370872</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>16729.029661</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>13607.129249</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>13.294779</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>78.45234000000001</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>199202098.8102723</v>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>RISK_OFF</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>15</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BANUSDT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Comedian</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>tradeability_marginal | btc_regime_caution | entry_chased</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>pullback_to_ema</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>68</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>MARGINAL</t>
+        </is>
+      </c>
+      <c r="N15" t="b">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.1355225963721603</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.16765</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>23.70630764748205</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>chased</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>0.1257953400014318</v>
+      </c>
+      <c r="T15" t="n">
+        <v>7.177590033780329</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.1452498527428888</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.1549771091136174</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.1647043654843459</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.09524376450978837</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>242.8176689</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>38.43508050000001</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>606.417869</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1961.302199</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>167369038.0239686</v>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>RISK_OFF</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>16</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>DEXEUSDT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DeXe</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>tradeability_marginal | btc_regime_caution | entry_chased</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>pullback_to_ema</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>68</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>MARGINAL</t>
+        </is>
+      </c>
+      <c r="N16" t="b">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5.124723018133185</v>
+      </c>
+      <c r="P16" t="n">
+        <v>5.423</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5.820353232972786</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>chased</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>4.764082143488518</v>
+      </c>
+      <c r="T16" t="n">
+        <v>7.037275446274556</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5.485363892777852</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.846004767422519</v>
+      </c>
+      <c r="W16" t="n">
+        <v>6.206645642067186</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.01842468908337787</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1576.27559</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2078.82757</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>141.258695</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>528.480269</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>453479867.3362362</v>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>RISK_OFF</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LAYERUSDT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Solayer</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>reversal</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>reversal_base_reclaim</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>61.168</v>
+      </c>
+      <c r="I17" t="n">
+        <v>76.45999999999999</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>MARGINAL</t>
+        </is>
+      </c>
+      <c r="N17" t="b">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.08553809548486238</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.08867999999999999</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.673105529563303</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>chased</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>0.07028</v>
+      </c>
+      <c r="T17" t="n">
+        <v>17.83777789109485</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.1007961909697248</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.1160542864545872</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.1313123819394496</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.1465036344170903</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>5267.2081632</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>9429.638013100001</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>38.684651</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>135.465016</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>35323932.13587327</v>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>RISK_OFF</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AG13"/>
+  <autoFilter ref="A1:AG17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/2026-03-17.xlsx
+++ b/reports/2026-03-17.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trade Candidates'!$A$1:$AG$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Enter Candidates'!$A$1:$AG$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wait Candidates'!$A$1:$AG$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Enter Candidates'!$A$1:$AG$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wait Candidates'!$A$1:$AG$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-17 15:51 UTC</t>
+          <t>2026-03-17 18:07 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
@@ -642,7 +642,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-03-17_1773762595579</t>
+          <t>2026-03-17_1773770772315</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>entry_late</t>
+          <t>entry_chased</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -956,14 +956,14 @@
         <v>3.570573042426071e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>3.633e-06</v>
+        <v>3.693e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.748373631687761</v>
+        <v>3.428776168957581</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>late</t>
+          <t>chased</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -988,22 +988,22 @@
         <v>2.000000000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.02752167331772813</v>
+        <v>0.05414185165133054</v>
       </c>
       <c r="AA2" t="n">
-        <v>831628.6260935001</v>
+        <v>695282.581372934</v>
       </c>
       <c r="AB2" t="n">
-        <v>568280.167103815</v>
+        <v>556406.04983398</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.201302</v>
+        <v>8.039870000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>14.914928</v>
+        <v>14.700338</v>
       </c>
       <c r="AE2" t="n">
-        <v>1503762547.232597</v>
+        <v>1528615478.925231</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -1018,22 +1018,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TRXUSDT</t>
+          <t>PUMPUSDT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TRON</t>
+          <t>Pump.fun</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>ENTER</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>effective_rr_insufficient | entry_chased</t>
+          <t>entry_chased</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>74.752</v>
+        <v>59.496</v>
       </c>
       <c r="I3" t="n">
-        <v>93.44</v>
+        <v>74.37</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -1070,13 +1070,13 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2893153896519431</v>
+        <v>0.002000494297826141</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3042</v>
+        <v>0.00209</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.144769646012826</v>
+        <v>4.474179320137073</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -1084,19 +1084,19 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0.268</v>
+        <v>0.001667</v>
       </c>
       <c r="T3" t="n">
-        <v>7.367527070573851</v>
+        <v>16.67059477192893</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3106307793038863</v>
+        <v>0.002333988595652282</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3319461689558294</v>
+        <v>0.002667482893478423</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3532615586077725</v>
+        <v>0.003000977191304564</v>
       </c>
       <c r="X3" t="n">
         <v>1</v>
@@ -1105,22 +1105,22 @@
         <v>2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.03287851389118675</v>
+        <v>0.04785833931561134</v>
       </c>
       <c r="AA3" t="n">
-        <v>1529175.661605</v>
+        <v>136315.96909223</v>
       </c>
       <c r="AB3" t="n">
-        <v>967099.6149340001</v>
+        <v>116786.06744769</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.643926</v>
+        <v>5.76251</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.643926</v>
+        <v>11.207548</v>
       </c>
       <c r="AE3" t="n">
-        <v>28807874085.95885</v>
+        <v>692585441.6912699</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
@@ -1190,10 +1190,10 @@
         <v>0.04320432927693411</v>
       </c>
       <c r="P4" t="n">
-        <v>0.04854</v>
+        <v>0.04911</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.34985199947196</v>
+        <v>13.66916422937923</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1222,22 +1222,22 @@
         <v>2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02058672156458286</v>
+        <v>0.02034381039569334</v>
       </c>
       <c r="AA4" t="n">
-        <v>19553.5759032</v>
+        <v>16176.4494677</v>
       </c>
       <c r="AB4" t="n">
-        <v>13143.0154511</v>
+        <v>7198.403133</v>
       </c>
       <c r="AC4" t="n">
-        <v>15.154426</v>
+        <v>20.813785</v>
       </c>
       <c r="AD4" t="n">
-        <v>354.823323</v>
+        <v>2030.946217</v>
       </c>
       <c r="AE4" t="n">
-        <v>139858424.4330002</v>
+        <v>141376491.5573838</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
         <v>5.764233529855139</v>
       </c>
       <c r="P5" t="n">
-        <v>6.619</v>
+        <v>6.734</v>
       </c>
       <c r="Q5" t="n">
-        <v>14.82879667726338</v>
+        <v>16.82385810918441</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1339,22 +1339,22 @@
         <v>2</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03019323671497252</v>
+        <v>0.01483349402952361</v>
       </c>
       <c r="AA5" t="n">
-        <v>7487.28291</v>
+        <v>26973.68621</v>
       </c>
       <c r="AB5" t="n">
-        <v>7368.29412</v>
+        <v>7603.55387</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.150932</v>
+        <v>21.539902</v>
       </c>
       <c r="AD5" t="n">
-        <v>410.330327</v>
+        <v>282.320348</v>
       </c>
       <c r="AE5" t="n">
-        <v>118483517.806406</v>
+        <v>119978315.9259302</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
         <v>0.003302794856571019</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003496</v>
+        <v>0.003533</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.849747011825235</v>
+        <v>6.970010352625455</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
         <v>1.999999999999999</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.171624713958808</v>
+        <v>0.1698273422020925</v>
       </c>
       <c r="AA6" t="n">
-        <v>15379.33683327</v>
+        <v>20801.07557487</v>
       </c>
       <c r="AB6" t="n">
-        <v>10728.90403699</v>
+        <v>12947.75535219</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.545616</v>
+        <v>18.334096</v>
       </c>
       <c r="AD6" t="n">
-        <v>92.307366</v>
+        <v>87.304671</v>
       </c>
       <c r="AE6" t="n">
-        <v>27258722.09736478</v>
+        <v>27414782.94131938</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
@@ -1541,10 +1541,10 @@
         <v>0.03091180535852996</v>
       </c>
       <c r="P7" t="n">
-        <v>0.035605</v>
+        <v>0.036554</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.18253168016592</v>
+        <v>18.25255618696211</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1573,22 +1573,22 @@
         <v>1.999999999999999</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1289382217737537</v>
+        <v>0.09795651818998478</v>
       </c>
       <c r="AA7" t="n">
-        <v>55967.13071129</v>
+        <v>16298.16718803</v>
       </c>
       <c r="AB7" t="n">
-        <v>20457.86793545</v>
+        <v>22783.47517579</v>
       </c>
       <c r="AC7" t="n">
-        <v>26.682585</v>
+        <v>17.567199</v>
       </c>
       <c r="AD7" t="n">
-        <v>51.172304</v>
+        <v>48.444275</v>
       </c>
       <c r="AE7" t="n">
-        <v>975806733.049776</v>
+        <v>996016384.2656837</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
@@ -1603,12 +1603,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ZECUSDT</t>
+          <t>MEUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Zcash</t>
+          <t>Magic Eden</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>effective_rr_insufficient | entry_chased</t>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1632,36 +1632,40 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>68.792</v>
+        <v>67.384</v>
       </c>
       <c r="I8" t="n">
-        <v>85.98999999999999</v>
+        <v>84.23</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N8" t="b">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>229.6644212431871</v>
+        <v>0.1190546835514273</v>
       </c>
       <c r="P8" t="n">
-        <v>268.65</v>
+        <v>0.124</v>
       </c>
       <c r="Q8" t="n">
-        <v>16.97501883216464</v>
+        <v>4.153819321552787</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1669,19 +1673,19 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>185</v>
+        <v>0.1106</v>
       </c>
       <c r="T8" t="n">
-        <v>19.44768850195251</v>
+        <v>7.101512766421464</v>
       </c>
       <c r="U8" t="n">
-        <v>274.3288424863741</v>
+        <v>0.1275093671028546</v>
       </c>
       <c r="V8" t="n">
-        <v>318.9932637295612</v>
+        <v>0.1359640506542819</v>
       </c>
       <c r="W8" t="n">
-        <v>363.6576849727483</v>
+        <v>0.1444187342057091</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
@@ -1690,22 +1694,22 @@
         <v>2</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.003721691881125777</v>
+        <v>0.08087343307723645</v>
       </c>
       <c r="AA8" t="n">
-        <v>117906.88669995</v>
+        <v>20983.493681</v>
       </c>
       <c r="AB8" t="n">
-        <v>71126.95808521</v>
+        <v>4966.382424</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.961808</v>
+        <v>26.725378</v>
       </c>
       <c r="AD8" t="n">
-        <v>11.554508</v>
+        <v>931.048091</v>
       </c>
       <c r="AE8" t="n">
-        <v>4445895174.543806</v>
+        <v>58529311.14516805</v>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
@@ -1720,12 +1724,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MEUSDT</t>
+          <t>BONKUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Magic Eden</t>
+          <t>Bonk</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1735,7 +1739,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1749,10 +1753,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>67.384</v>
+        <v>65.72799999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>84.23</v>
+        <v>82.16</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1764,25 +1768,25 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N9" t="b">
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1190546835514273</v>
+        <v>6.116580042993848e-06</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1228</v>
+        <v>6.523e-06</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.145879134570029</v>
+        <v>6.644562061632464</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1790,19 +1794,19 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>0.1106</v>
+        <v>5.135e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>7.101512766421464</v>
+        <v>16.04785739897551</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1275093671028546</v>
+        <v>7.098160085987695e-06</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1359640506542819</v>
+        <v>8.079740128981543e-06</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1444187342057091</v>
+        <v>9.061320171975392e-06</v>
       </c>
       <c r="X9" t="n">
         <v>1</v>
@@ -1811,22 +1815,22 @@
         <v>2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.08146639511201863</v>
+        <v>0.1073043611558228</v>
       </c>
       <c r="AA9" t="n">
-        <v>12477.055833</v>
+        <v>161634.337641281</v>
       </c>
       <c r="AB9" t="n">
-        <v>3565.75736</v>
+        <v>197165.25694702</v>
       </c>
       <c r="AC9" t="n">
-        <v>75.454998</v>
+        <v>10.638869</v>
       </c>
       <c r="AD9" t="n">
-        <v>2144.978265</v>
+        <v>11.282375</v>
       </c>
       <c r="AE9" t="n">
-        <v>58110891.25980759</v>
+        <v>573501277.5872406</v>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
@@ -1841,12 +1845,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ZKUSDT</t>
+          <t>RLCUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ZKsync</t>
+          <t>iExec RLC</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1856,7 +1860,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1870,10 +1874,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>66.392</v>
+        <v>65.584</v>
       </c>
       <c r="I10" t="n">
-        <v>82.98999999999999</v>
+        <v>81.98</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1885,25 +1889,25 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N10" t="b">
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01959585256778836</v>
+        <v>0.4023141535192251</v>
       </c>
       <c r="P10" t="n">
-        <v>0.02087</v>
+        <v>0.4486</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.50212807941859</v>
+        <v>11.50490135032325</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1911,43 +1915,43 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>0.01778</v>
+        <v>0.3518</v>
       </c>
       <c r="T10" t="n">
-        <v>9.266514745948117</v>
+        <v>12.55589769272465</v>
       </c>
       <c r="U10" t="n">
-        <v>0.02141170513557672</v>
+        <v>0.4528283070384502</v>
       </c>
       <c r="V10" t="n">
-        <v>0.02322755770336508</v>
+        <v>0.5033424605576753</v>
       </c>
       <c r="W10" t="n">
-        <v>0.02504341027115345</v>
+        <v>0.5538566140769005</v>
       </c>
       <c r="X10" t="n">
         <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>2</v>
+        <v>1.999999999999999</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.04783544606554921</v>
+        <v>0.2229157378510925</v>
       </c>
       <c r="AA10" t="n">
-        <v>47274.4740612</v>
+        <v>10194.378273</v>
       </c>
       <c r="AB10" t="n">
-        <v>58380.6843272</v>
+        <v>6876.836912</v>
       </c>
       <c r="AC10" t="n">
-        <v>22.622443</v>
+        <v>49.057711</v>
       </c>
       <c r="AD10" t="n">
-        <v>39.779511</v>
+        <v>255.691991</v>
       </c>
       <c r="AE10" t="n">
-        <v>193921738.6876874</v>
+        <v>39180178.05127673</v>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
@@ -1962,12 +1966,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MUSDT</t>
+          <t>NEOUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MemeCore</t>
+          <t>Neo</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1977,29 +1981,33 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>tradeability_marginal | btc_regime_caution | entry_chased</t>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>breakout</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>fresh_breakout</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>66.03616599999999</v>
+        <v>62.24</v>
       </c>
       <c r="I11" t="n">
-        <v>66.03616599999999</v>
+        <v>77.8</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>none</t>
@@ -2014,13 +2022,13 @@
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.56624</v>
+        <v>2.663747724979867</v>
       </c>
       <c r="P11" t="n">
-        <v>1.74695</v>
+        <v>2.873</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.5378230667075</v>
+        <v>7.855559032780213</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2028,19 +2036,19 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>1.485268466728675</v>
+        <v>2.419</v>
       </c>
       <c r="T11" t="n">
-        <v>5.169803687259019</v>
+        <v>9.188097006510514</v>
       </c>
       <c r="U11" t="n">
-        <v>1.647211533271326</v>
+        <v>2.908495449959734</v>
       </c>
       <c r="V11" t="n">
-        <v>1.728183066542652</v>
+        <v>3.153243174939601</v>
       </c>
       <c r="W11" t="n">
-        <v>1.809154599813977</v>
+        <v>3.397990899919468</v>
       </c>
       <c r="X11" t="n">
         <v>1</v>
@@ -2049,22 +2057,22 @@
         <v>2</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.1257796911536845</v>
+        <v>0.03480076561683974</v>
       </c>
       <c r="AA11" t="n">
-        <v>4020.179897</v>
+        <v>23935.640413</v>
       </c>
       <c r="AB11" t="n">
-        <v>6949.0029706</v>
+        <v>12162.162051</v>
       </c>
       <c r="AC11" t="n">
-        <v>22.15674</v>
+        <v>16.127085</v>
       </c>
       <c r="AD11" t="n">
-        <v>1051.641306</v>
+        <v>581.822193</v>
       </c>
       <c r="AE11" t="n">
-        <v>2233919070.459943</v>
+        <v>201976367.3374268</v>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
@@ -2079,12 +2087,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BONKUSDT</t>
+          <t>DEXEUSDT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bonk</t>
+          <t>DeXe</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2094,54 +2102,50 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>65.72799999999999</v>
+        <v>61.2</v>
       </c>
       <c r="I12" t="n">
-        <v>82.16</v>
+        <v>68</v>
       </c>
       <c r="J12" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N12" t="b">
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>6.116580042993848e-06</v>
+        <v>5.160273207392032</v>
       </c>
       <c r="P12" t="n">
-        <v>6.426e-06</v>
+        <v>5.652</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.058708540249923</v>
+        <v>9.529084465984772</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -2149,19 +2153,19 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>5.135e-06</v>
+        <v>4.79281843420018</v>
       </c>
       <c r="T12" t="n">
-        <v>16.04785739897551</v>
+        <v>7.120839506433045</v>
       </c>
       <c r="U12" t="n">
-        <v>7.098160085987695e-06</v>
+        <v>5.527727980583883</v>
       </c>
       <c r="V12" t="n">
-        <v>8.079740128981543e-06</v>
+        <v>5.895182753775734</v>
       </c>
       <c r="W12" t="n">
-        <v>9.061320171975392e-06</v>
+        <v>6.262637526967586</v>
       </c>
       <c r="X12" t="n">
         <v>1</v>
@@ -2170,22 +2174,22 @@
         <v>2</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.1243008079552479</v>
+        <v>0.07090941322459776</v>
       </c>
       <c r="AA12" t="n">
-        <v>141446.879968649</v>
+        <v>3117.51048</v>
       </c>
       <c r="AB12" t="n">
-        <v>104208.376136778</v>
+        <v>1664.1054</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.21504</v>
+        <v>125.532636</v>
       </c>
       <c r="AD12" t="n">
-        <v>15.512563</v>
+        <v>226.913423</v>
       </c>
       <c r="AE12" t="n">
-        <v>566117408.0313501</v>
+        <v>471213956.3932709</v>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
@@ -2200,12 +2204,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RLCUSDT</t>
+          <t>HYPERUSDT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iExec RLC</t>
+          <t>Hyperlane</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2229,10 +2233,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>65.584</v>
+        <v>61.072</v>
       </c>
       <c r="I13" t="n">
-        <v>81.98</v>
+        <v>76.34</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -2256,13 +2260,13 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4023141535192251</v>
+        <v>0.0923388600951853</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4497</v>
+        <v>0.10873</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.77831952126698</v>
+        <v>17.75107456158576</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -2270,43 +2274,43 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>0.3518</v>
+        <v>0.07989</v>
       </c>
       <c r="T13" t="n">
-        <v>12.55589769272465</v>
+        <v>13.48171298882473</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4528283070384502</v>
+        <v>0.1047877201903706</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5033424605576753</v>
+        <v>0.1172365802855559</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5538566140769005</v>
+        <v>0.1296854403807412</v>
       </c>
       <c r="X13" t="n">
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.999999999999999</v>
+        <v>2</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.2880248144455574</v>
+        <v>0.1103549751701261</v>
       </c>
       <c r="AA13" t="n">
-        <v>6555.92775</v>
+        <v>10067.1510832</v>
       </c>
       <c r="AB13" t="n">
-        <v>8224.385313999999</v>
+        <v>9264.219072800001</v>
       </c>
       <c r="AC13" t="n">
-        <v>35.660819</v>
+        <v>35.716808</v>
       </c>
       <c r="AD13" t="n">
-        <v>236.555748</v>
+        <v>149.145773</v>
       </c>
       <c r="AE13" t="n">
-        <v>39230827.60174326</v>
+        <v>25475599.87319592</v>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
@@ -2321,12 +2325,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ACHUSDT</t>
+          <t>ETHUSDT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Alchemy Pay</t>
+          <t>Ethereum</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2336,7 +2340,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>effective_rr_insufficient | entry_chased</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2350,40 +2354,36 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>63.152</v>
+        <v>60.056</v>
       </c>
       <c r="I14" t="n">
-        <v>78.94</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="J14" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N14" t="b">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.007042603236678154</v>
+        <v>2080.287972457166</v>
       </c>
       <c r="P14" t="n">
-        <v>0.007514</v>
+        <v>2337.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.69350164250051</v>
+        <v>12.36905807992079</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -2391,43 +2391,43 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>0.006221</v>
+        <v>1750</v>
       </c>
       <c r="T14" t="n">
-        <v>11.66618662257178</v>
+        <v>15.8770312971161</v>
       </c>
       <c r="U14" t="n">
-        <v>0.007864206473356308</v>
+        <v>2410.575944914332</v>
       </c>
       <c r="V14" t="n">
-        <v>0.008685809710034463</v>
+        <v>2740.863917371499</v>
       </c>
       <c r="W14" t="n">
-        <v>0.009507412946712618</v>
+        <v>3071.151889828665</v>
       </c>
       <c r="X14" t="n">
-        <v>0.9999999999999989</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
         <v>2</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.1998534408100645</v>
+        <v>0.0004277004471701533</v>
       </c>
       <c r="AA14" t="n">
-        <v>17121.81179649</v>
+        <v>266380.4482861</v>
       </c>
       <c r="AB14" t="n">
-        <v>5001.72296197</v>
+        <v>602134.7222113</v>
       </c>
       <c r="AC14" t="n">
-        <v>67.692263</v>
+        <v>0.344305</v>
       </c>
       <c r="AD14" t="n">
-        <v>278.244895</v>
+        <v>0.42289</v>
       </c>
       <c r="AE14" t="n">
-        <v>75299172.72841798</v>
+        <v>282493405473.6589</v>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NEOUSDT</t>
+          <t>ZETAUSDT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Neo</t>
+          <t>ZetaChain</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>62.24</v>
+        <v>59.312</v>
       </c>
       <c r="I15" t="n">
-        <v>77.8</v>
+        <v>74.14</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2498,13 +2498,13 @@
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>2.663747724979867</v>
+        <v>0.05178030231565991</v>
       </c>
       <c r="P15" t="n">
-        <v>2.823</v>
+        <v>0.0561</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.978504402902352</v>
+        <v>8.342357018324487</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -2512,43 +2512,43 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>2.419</v>
+        <v>0.04527</v>
       </c>
       <c r="T15" t="n">
-        <v>9.188097006510514</v>
+        <v>12.57293222425046</v>
       </c>
       <c r="U15" t="n">
-        <v>2.908495449959734</v>
+        <v>0.05829060463131982</v>
       </c>
       <c r="V15" t="n">
-        <v>3.153243174939601</v>
+        <v>0.06480090694697974</v>
       </c>
       <c r="W15" t="n">
-        <v>3.397990899919468</v>
+        <v>0.07131120926263965</v>
       </c>
       <c r="X15" t="n">
         <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>2</v>
+        <v>2.000000000000001</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.03539196602370872</v>
+        <v>0.05341404789460028</v>
       </c>
       <c r="AA15" t="n">
-        <v>16729.029661</v>
+        <v>3140.8736058</v>
       </c>
       <c r="AB15" t="n">
-        <v>13607.129249</v>
+        <v>3168.0047436</v>
       </c>
       <c r="AC15" t="n">
-        <v>13.294779</v>
+        <v>1620.676888</v>
       </c>
       <c r="AD15" t="n">
-        <v>78.45234000000001</v>
+        <v>16346.801126</v>
       </c>
       <c r="AE15" t="n">
-        <v>199202098.8102723</v>
+        <v>73898404.18888804</v>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
@@ -2563,39 +2563,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BANUSDT</t>
+          <t>ASTERUSDT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Comedian</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>NO_TRADE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>tradeability_marginal | btc_regime_caution | entry_chased</t>
+          <t>risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>61.2</v>
+        <v>69.16</v>
       </c>
       <c r="I16" t="n">
-        <v>68</v>
+        <v>86.45</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
@@ -2603,25 +2603,25 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1355225963721603</v>
+        <v>0.7055770637341362</v>
       </c>
       <c r="P16" t="n">
-        <v>0.16765</v>
+        <v>0.7652</v>
       </c>
       <c r="Q16" t="n">
-        <v>23.70630764748205</v>
+        <v>8.450237306513397</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -2629,43 +2629,43 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>0.1257953400014318</v>
+        <v>0.404</v>
       </c>
       <c r="T16" t="n">
-        <v>7.177590033780329</v>
+        <v>42.74190293801436</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1452498527428888</v>
+        <v>1.007154127468272</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1549771091136174</v>
+        <v>1.308731191202408</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1647043654843459</v>
+        <v>1.610308254936545</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>0.9999999999999997</v>
       </c>
       <c r="Y16" t="n">
         <v>2</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.09524376450978837</v>
+        <v>0.06538939384032642</v>
       </c>
       <c r="AA16" t="n">
-        <v>242.8176689</v>
+        <v>248144.435038</v>
       </c>
       <c r="AB16" t="n">
-        <v>38.43508050000001</v>
+        <v>236621.781709</v>
       </c>
       <c r="AC16" t="n">
-        <v>606.417869</v>
+        <v>5.584852</v>
       </c>
       <c r="AD16" t="n">
-        <v>1961.302199</v>
+        <v>5.809995</v>
       </c>
       <c r="AE16" t="n">
-        <v>167369038.0239686</v>
+        <v>1900005954.028785</v>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
@@ -2680,39 +2680,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DEXEUSDT</t>
+          <t>ZECUSDT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DeXe</t>
+          <t>Zcash</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>NO_TRADE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>tradeability_marginal | btc_regime_caution | entry_chased</t>
+          <t>price_past_target_1 | entry_chased</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>61.2</v>
+        <v>68.792</v>
       </c>
       <c r="I17" t="n">
-        <v>68</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
@@ -2720,25 +2720,25 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N17" t="b">
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>5.124723018133185</v>
+        <v>229.6644212431871</v>
       </c>
       <c r="P17" t="n">
-        <v>5.423</v>
+        <v>283.82</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.820353232972786</v>
+        <v>23.58030837500453</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -2746,19 +2746,19 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>4.764082143488518</v>
+        <v>185</v>
       </c>
       <c r="T17" t="n">
-        <v>7.037275446274556</v>
+        <v>19.44768850195251</v>
       </c>
       <c r="U17" t="n">
-        <v>5.485363892777852</v>
+        <v>274.3288424863741</v>
       </c>
       <c r="V17" t="n">
-        <v>5.846004767422519</v>
+        <v>318.9932637295612</v>
       </c>
       <c r="W17" t="n">
-        <v>6.206645642067186</v>
+        <v>363.6576849727483</v>
       </c>
       <c r="X17" t="n">
         <v>1</v>
@@ -2767,22 +2767,22 @@
         <v>2</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.01842468908337787</v>
+        <v>0.02460413700989198</v>
       </c>
       <c r="AA17" t="n">
-        <v>1576.27559</v>
+        <v>113314.97360884</v>
       </c>
       <c r="AB17" t="n">
-        <v>2078.82757</v>
+        <v>55407.09419894</v>
       </c>
       <c r="AC17" t="n">
-        <v>141.258695</v>
+        <v>6.866252</v>
       </c>
       <c r="AD17" t="n">
-        <v>528.480269</v>
+        <v>17.176807</v>
       </c>
       <c r="AE17" t="n">
-        <v>453479867.3362362</v>
+        <v>4648046575.439239</v>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
@@ -2797,69 +2797,65 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LAYERUSDT</t>
+          <t>HYPEUSDT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Solayer</t>
+          <t>Hyperliquid</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>NO_TRADE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>risk_reward_unattractive | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>breakout</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>confirmed_breakout</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>61.168</v>
+        <v>65.856717</v>
       </c>
       <c r="I18" t="n">
-        <v>76.45999999999999</v>
+        <v>65.856717</v>
       </c>
       <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>DIRECT_OK</t>
+        </is>
+      </c>
+      <c r="N18" t="b">
         <v>0</v>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>MARGINAL</t>
-        </is>
-      </c>
-      <c r="N18" t="b">
-        <v>1</v>
-      </c>
       <c r="O18" t="n">
-        <v>0.08553809548486238</v>
+        <v>38.86</v>
       </c>
       <c r="P18" t="n">
-        <v>0.08867999999999999</v>
+        <v>40.37</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.673105529563303</v>
+        <v>3.885743695316513</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -2867,19 +2863,19 @@
         </is>
       </c>
       <c r="S18" t="n">
-        <v>0.07028</v>
+        <v>34.11745653141787</v>
       </c>
       <c r="T18" t="n">
-        <v>17.83777789109485</v>
+        <v>12.20417773695864</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1007961909697248</v>
+        <v>43.60254346858213</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1160542864545872</v>
+        <v>48.34508693716425</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1313123819394496</v>
+        <v>53.08763040574638</v>
       </c>
       <c r="X18" t="n">
         <v>1</v>
@@ -2888,22 +2884,22 @@
         <v>2</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.1465036344170903</v>
+        <v>0.0495172072295024</v>
       </c>
       <c r="AA18" t="n">
-        <v>5267.2081632</v>
+        <v>59436.546</v>
       </c>
       <c r="AB18" t="n">
-        <v>9429.638013100001</v>
+        <v>93988.85890000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>38.684651</v>
+        <v>8.201847000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>135.465016</v>
+        <v>12.586757</v>
       </c>
       <c r="AE18" t="n">
-        <v>35323932.13587327</v>
+        <v>10402525935.79681</v>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
@@ -2918,12 +2914,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IMXUSDT</t>
+          <t>LINKUSDT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Immutable</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2933,7 +2929,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2947,10 +2943,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>73.968</v>
+        <v>65.56</v>
       </c>
       <c r="I19" t="n">
-        <v>92.45999999999999</v>
+        <v>81.95</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
@@ -2958,25 +2954,25 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N19" t="b">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1650630349830551</v>
+        <v>9.105111163632445</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1783</v>
+        <v>9.887</v>
       </c>
       <c r="Q19" t="n">
-        <v>8.019339410731053</v>
+        <v>8.58736178302324</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -2984,19 +2980,19 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>0.1288</v>
+        <v>7.16</v>
       </c>
       <c r="T19" t="n">
-        <v>21.96920405999909</v>
+        <v>21.36284915885037</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2013260699661101</v>
+        <v>11.05022232726489</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2375891049491652</v>
+        <v>12.99533349089734</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2738521399322202</v>
+        <v>14.94044465452978</v>
       </c>
       <c r="X19" t="n">
         <v>1</v>
@@ -3005,22 +3001,22 @@
         <v>2</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.056038105912014</v>
+        <v>0.01011275724325677</v>
       </c>
       <c r="AA19" t="n">
-        <v>12869.873846</v>
+        <v>1179004.69301</v>
       </c>
       <c r="AB19" t="n">
-        <v>11686.979658</v>
+        <v>1295303.87553</v>
       </c>
       <c r="AC19" t="n">
-        <v>27.432788</v>
+        <v>1.532857</v>
       </c>
       <c r="AD19" t="n">
-        <v>204.391727</v>
+        <v>2.279338</v>
       </c>
       <c r="AE19" t="n">
-        <v>354967033.4957088</v>
+        <v>7000908611.659738</v>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
@@ -3035,12 +3031,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HYPEUSDT</t>
+          <t>XMRUSDT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hyperliquid</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3050,24 +3046,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | btc_regime_caution | entry_late</t>
+          <t>risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>breakout</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>confirmed_breakout</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>69.841424</v>
+        <v>64.944</v>
       </c>
       <c r="I20" t="n">
-        <v>69.841424</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
@@ -3087,33 +3083,33 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>38.86</v>
+        <v>351.787693115702</v>
       </c>
       <c r="P20" t="n">
-        <v>39.72</v>
+        <v>370.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.213072568193519</v>
+        <v>5.248138933110935</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>late</t>
+          <t>chased</t>
         </is>
       </c>
       <c r="S20" t="n">
-        <v>34.11745653141787</v>
+        <v>276.36</v>
       </c>
       <c r="T20" t="n">
-        <v>12.20417773695864</v>
+        <v>21.44125408357991</v>
       </c>
       <c r="U20" t="n">
-        <v>43.60254346858213</v>
+        <v>427.2153862314041</v>
       </c>
       <c r="V20" t="n">
-        <v>48.34508693716425</v>
+        <v>502.6430793471061</v>
       </c>
       <c r="W20" t="n">
-        <v>53.08763040574638</v>
+        <v>578.0707724628081</v>
       </c>
       <c r="X20" t="n">
         <v>1</v>
@@ -3122,22 +3118,22 @@
         <v>2</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.0251667295835035</v>
+        <v>0.1051312118394035</v>
       </c>
       <c r="AA20" t="n">
-        <v>77037.26669999999</v>
+        <v>148328.09304</v>
       </c>
       <c r="AB20" t="n">
-        <v>81424.85770000001</v>
+        <v>119593.55655</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.390817</v>
+        <v>12.378847</v>
       </c>
       <c r="AD20" t="n">
-        <v>11.910691</v>
+        <v>17.445408</v>
       </c>
       <c r="AE20" t="n">
-        <v>10207919597.19811</v>
+        <v>6824278425.56964</v>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
@@ -3152,12 +3148,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LINKUSDT</t>
+          <t>SUIUSDT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Sui</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3167,24 +3163,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | entry_chased</t>
+          <t>risk_reward_unattractive | entry_late</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>65.56</v>
+        <v>58.32</v>
       </c>
       <c r="I21" t="n">
-        <v>81.95</v>
+        <v>64.8</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
@@ -3204,57 +3200,57 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>9.105111163632445</v>
+        <v>1.026230023869264</v>
       </c>
       <c r="P21" t="n">
-        <v>9.757</v>
+        <v>1.0312</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.15959228451073</v>
+        <v>0.4842945553276135</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>chased</t>
+          <t>late</t>
         </is>
       </c>
       <c r="S21" t="n">
-        <v>7.16</v>
+        <v>0.9982990087660092</v>
       </c>
       <c r="T21" t="n">
-        <v>21.36284915885037</v>
+        <v>2.721710966703596</v>
       </c>
       <c r="U21" t="n">
-        <v>11.05022232726489</v>
+        <v>1.054161038972519</v>
       </c>
       <c r="V21" t="n">
-        <v>12.99533349089734</v>
+        <v>1.082092054075773</v>
       </c>
       <c r="W21" t="n">
-        <v>14.94044465452978</v>
+        <v>1.110023069179028</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.000000000000004</v>
       </c>
       <c r="Y21" t="n">
         <v>2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.01024222870896139</v>
+        <v>0.00969696969699016</v>
       </c>
       <c r="AA21" t="n">
-        <v>926758.89771</v>
+        <v>339501.439979</v>
       </c>
       <c r="AB21" t="n">
-        <v>945394.59074</v>
+        <v>309651.436116</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.404793</v>
+        <v>2.071269</v>
       </c>
       <c r="AD21" t="n">
-        <v>5.562133</v>
+        <v>3.300006</v>
       </c>
       <c r="AE21" t="n">
-        <v>6917834477.289282</v>
+        <v>4020387482.757254</v>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
@@ -3275,7 +3271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:AG3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3501,7 +3497,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>entry_late</t>
+          <t>entry_chased</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3541,14 +3537,14 @@
         <v>3.570573042426071e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>3.633e-06</v>
+        <v>3.693e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.748373631687761</v>
+        <v>3.428776168957581</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>late</t>
+          <t>chased</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -3573,22 +3569,22 @@
         <v>2.000000000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.02752167331772813</v>
+        <v>0.05414185165133054</v>
       </c>
       <c r="AA2" t="n">
-        <v>831628.6260935001</v>
+        <v>695282.581372934</v>
       </c>
       <c r="AB2" t="n">
-        <v>568280.167103815</v>
+        <v>556406.04983398</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.201302</v>
+        <v>8.039870000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>14.914928</v>
+        <v>14.700338</v>
       </c>
       <c r="AE2" t="n">
-        <v>1503762547.232597</v>
+        <v>1528615478.925231</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -3597,8 +3593,125 @@
       </c>
       <c r="AG2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PUMPUSDT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Pump.fun</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ENTER</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>entry_chased</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>reversal</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>reversal_base_reclaim</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>59.496</v>
+      </c>
+      <c r="I3" t="n">
+        <v>74.37</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>DIRECT_OK</t>
+        </is>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.002000494297826141</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.00209</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4.474179320137073</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>chased</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0.001667</v>
+      </c>
+      <c r="T3" t="n">
+        <v>16.67059477192893</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.002333988595652282</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.002667482893478423</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.003000977191304564</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.04785833931561134</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>136315.96909223</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>116786.06744769</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>5.76251</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>11.207548</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>692585441.6912699</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>RISK_OFF</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AG2"/>
+  <autoFilter ref="A1:AG3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3609,7 +3722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG17"/>
+  <dimension ref="A1:AG13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3816,16 +3929,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TRXUSDT</t>
+          <t>SUSDT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TRON</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3835,7 +3948,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>effective_rr_insufficient | entry_chased</t>
+          <t>tradeability_marginal | entry_chased</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3849,10 +3962,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>74.752</v>
+        <v>73.032</v>
       </c>
       <c r="I2" t="n">
-        <v>93.44</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -3860,25 +3973,25 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N2" t="b">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2893153896519431</v>
+        <v>0.04320432927693411</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3042</v>
+        <v>0.04911</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.144769646012826</v>
+        <v>13.66916422937923</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -3886,19 +3999,19 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>0.268</v>
+        <v>0.03667</v>
       </c>
       <c r="T2" t="n">
-        <v>7.367527070573851</v>
+        <v>15.12424654263213</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3106307793038863</v>
+        <v>0.04973865855386821</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3319461689558294</v>
+        <v>0.05627298783080232</v>
       </c>
       <c r="W2" t="n">
-        <v>0.3532615586077725</v>
+        <v>0.06280731710773643</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
@@ -3907,22 +4020,22 @@
         <v>2</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.03287851389118675</v>
+        <v>0.02034381039569334</v>
       </c>
       <c r="AA2" t="n">
-        <v>1529175.661605</v>
+        <v>16176.4494677</v>
       </c>
       <c r="AB2" t="n">
-        <v>967099.6149340001</v>
+        <v>7198.403133</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.643926</v>
+        <v>20.813785</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.643926</v>
+        <v>2030.946217</v>
       </c>
       <c r="AE2" t="n">
-        <v>28807874085.95885</v>
+        <v>141376491.5573838</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -3933,16 +4046,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SUSDT</t>
+          <t>ZENUSDT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>Horizen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3966,10 +4079,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>73.032</v>
+        <v>72.104</v>
       </c>
       <c r="I3" t="n">
-        <v>91.29000000000001</v>
+        <v>90.13</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -3989,13 +4102,13 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04320432927693411</v>
+        <v>5.764233529855139</v>
       </c>
       <c r="P3" t="n">
-        <v>0.04854</v>
+        <v>6.734</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.34985199947196</v>
+        <v>16.82385810918441</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -4003,19 +4116,19 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0.03667</v>
+        <v>4.94</v>
       </c>
       <c r="T3" t="n">
-        <v>15.12424654263213</v>
+        <v>14.29910022878363</v>
       </c>
       <c r="U3" t="n">
-        <v>0.04973865855386821</v>
+        <v>6.588467059710278</v>
       </c>
       <c r="V3" t="n">
-        <v>0.05627298783080232</v>
+        <v>7.412700589565417</v>
       </c>
       <c r="W3" t="n">
-        <v>0.06280731710773643</v>
+        <v>8.236934119420557</v>
       </c>
       <c r="X3" t="n">
         <v>1</v>
@@ -4024,22 +4137,22 @@
         <v>2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.02058672156458286</v>
+        <v>0.01483349402952361</v>
       </c>
       <c r="AA3" t="n">
-        <v>19553.5759032</v>
+        <v>26973.68621</v>
       </c>
       <c r="AB3" t="n">
-        <v>13143.0154511</v>
+        <v>7603.55387</v>
       </c>
       <c r="AC3" t="n">
-        <v>15.154426</v>
+        <v>21.539902</v>
       </c>
       <c r="AD3" t="n">
-        <v>354.823323</v>
+        <v>282.320348</v>
       </c>
       <c r="AE3" t="n">
-        <v>139858424.4330002</v>
+        <v>119978315.9259302</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
@@ -4050,16 +4163,16 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ZENUSDT</t>
+          <t>REZUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Horizen</t>
+          <t>Renzo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4083,10 +4196,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>72.104</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>90.13</v>
+        <v>89.7</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -4106,13 +4219,13 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>5.764233529855139</v>
+        <v>0.003302794856571019</v>
       </c>
       <c r="P4" t="n">
-        <v>6.619</v>
+        <v>0.003533</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.82879667726338</v>
+        <v>6.970010352625455</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -4120,43 +4233,43 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>4.94</v>
+        <v>0.002644</v>
       </c>
       <c r="T4" t="n">
-        <v>14.29910022878363</v>
+        <v>19.94658721416878</v>
       </c>
       <c r="U4" t="n">
-        <v>6.588467059710278</v>
+        <v>0.003961589713142038</v>
       </c>
       <c r="V4" t="n">
-        <v>7.412700589565417</v>
+        <v>0.004620384569713056</v>
       </c>
       <c r="W4" t="n">
-        <v>8.236934119420557</v>
+        <v>0.005279179426284076</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>2</v>
+        <v>1.999999999999999</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03019323671497252</v>
+        <v>0.1698273422020925</v>
       </c>
       <c r="AA4" t="n">
-        <v>7487.28291</v>
+        <v>20801.07557487</v>
       </c>
       <c r="AB4" t="n">
-        <v>7368.29412</v>
+        <v>12947.75535219</v>
       </c>
       <c r="AC4" t="n">
-        <v>18.150932</v>
+        <v>18.334096</v>
       </c>
       <c r="AD4" t="n">
-        <v>410.330327</v>
+        <v>87.304671</v>
       </c>
       <c r="AE4" t="n">
-        <v>118483517.806406</v>
+        <v>27414782.94131938</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
@@ -4167,16 +4280,16 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>REZUSDT</t>
+          <t>KASUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Renzo</t>
+          <t>Kaspa</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4200,10 +4313,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>71.76000000000001</v>
+        <v>70.328</v>
       </c>
       <c r="I5" t="n">
-        <v>89.7</v>
+        <v>87.91</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -4223,13 +4336,13 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.003302794856571019</v>
+        <v>0.03091180535852996</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003496</v>
+        <v>0.036554</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.849747011825235</v>
+        <v>18.25255618696211</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -4237,19 +4350,19 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0.002644</v>
+        <v>0.025188</v>
       </c>
       <c r="T5" t="n">
-        <v>19.94658721416878</v>
+        <v>18.51656767420252</v>
       </c>
       <c r="U5" t="n">
-        <v>0.003961589713142038</v>
+        <v>0.03663561071705992</v>
       </c>
       <c r="V5" t="n">
-        <v>0.004620384569713056</v>
+        <v>0.04235941607558988</v>
       </c>
       <c r="W5" t="n">
-        <v>0.005279179426284076</v>
+        <v>0.04808322143411985</v>
       </c>
       <c r="X5" t="n">
         <v>1.000000000000001</v>
@@ -4258,22 +4371,22 @@
         <v>1.999999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.171624713958808</v>
+        <v>0.09795651818998478</v>
       </c>
       <c r="AA5" t="n">
-        <v>15379.33683327</v>
+        <v>16298.16718803</v>
       </c>
       <c r="AB5" t="n">
-        <v>10728.90403699</v>
+        <v>22783.47517579</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.545616</v>
+        <v>17.567199</v>
       </c>
       <c r="AD5" t="n">
-        <v>92.307366</v>
+        <v>48.444275</v>
       </c>
       <c r="AE5" t="n">
-        <v>27258722.09736478</v>
+        <v>996016384.2656837</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
@@ -4284,16 +4397,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KASUSDT</t>
+          <t>MEUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kaspa</t>
+          <t>Magic Eden</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4303,7 +4416,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_chased</t>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4317,15 +4430,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>70.328</v>
+        <v>67.384</v>
       </c>
       <c r="I6" t="n">
-        <v>87.91</v>
+        <v>84.23</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>none</t>
@@ -4340,13 +4457,13 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03091180535852996</v>
+        <v>0.1190546835514273</v>
       </c>
       <c r="P6" t="n">
-        <v>0.035605</v>
+        <v>0.124</v>
       </c>
       <c r="Q6" t="n">
-        <v>15.18253168016592</v>
+        <v>4.153819321552787</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -4354,43 +4471,43 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>0.025188</v>
+        <v>0.1106</v>
       </c>
       <c r="T6" t="n">
-        <v>18.51656767420252</v>
+        <v>7.101512766421464</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03663561071705992</v>
+        <v>0.1275093671028546</v>
       </c>
       <c r="V6" t="n">
-        <v>0.04235941607558988</v>
+        <v>0.1359640506542819</v>
       </c>
       <c r="W6" t="n">
-        <v>0.04808322143411985</v>
+        <v>0.1444187342057091</v>
       </c>
       <c r="X6" t="n">
-        <v>1.000000000000001</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.999999999999999</v>
+        <v>2</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.1289382217737537</v>
+        <v>0.08087343307723645</v>
       </c>
       <c r="AA6" t="n">
-        <v>55967.13071129</v>
+        <v>20983.493681</v>
       </c>
       <c r="AB6" t="n">
-        <v>20457.86793545</v>
+        <v>4966.382424</v>
       </c>
       <c r="AC6" t="n">
-        <v>26.682585</v>
+        <v>26.725378</v>
       </c>
       <c r="AD6" t="n">
-        <v>51.172304</v>
+        <v>931.048091</v>
       </c>
       <c r="AE6" t="n">
-        <v>975806733.049776</v>
+        <v>58529311.14516805</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
@@ -4401,16 +4518,16 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ZECUSDT</t>
+          <t>BONKUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Zcash</t>
+          <t>Bonk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4420,7 +4537,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>effective_rr_insufficient | entry_chased</t>
+          <t>entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4434,15 +4551,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>68.792</v>
+        <v>65.72799999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>85.98999999999999</v>
+        <v>82.16</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>direct</t>
@@ -4457,13 +4578,13 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>229.6644212431871</v>
+        <v>6.116580042993848e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>268.65</v>
+        <v>6.523e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>16.97501883216464</v>
+        <v>6.644562061632464</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -4471,19 +4592,19 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>185</v>
+        <v>5.135e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>19.44768850195251</v>
+        <v>16.04785739897551</v>
       </c>
       <c r="U7" t="n">
-        <v>274.3288424863741</v>
+        <v>7.098160085987695e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>318.9932637295612</v>
+        <v>8.079740128981543e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>363.6576849727483</v>
+        <v>9.061320171975392e-06</v>
       </c>
       <c r="X7" t="n">
         <v>1</v>
@@ -4492,22 +4613,22 @@
         <v>2</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.003721691881125777</v>
+        <v>0.1073043611558228</v>
       </c>
       <c r="AA7" t="n">
-        <v>117906.88669995</v>
+        <v>161634.337641281</v>
       </c>
       <c r="AB7" t="n">
-        <v>71126.95808521</v>
+        <v>197165.25694702</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.961808</v>
+        <v>10.638869</v>
       </c>
       <c r="AD7" t="n">
-        <v>11.554508</v>
+        <v>11.282375</v>
       </c>
       <c r="AE7" t="n">
-        <v>4445895174.543806</v>
+        <v>573501277.5872406</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
@@ -4518,16 +4639,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MEUSDT</t>
+          <t>RLCUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Magic Eden</t>
+          <t>iExec RLC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4551,10 +4672,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>67.384</v>
+        <v>65.584</v>
       </c>
       <c r="I8" t="n">
-        <v>84.23</v>
+        <v>81.98</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -4578,13 +4699,13 @@
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1190546835514273</v>
+        <v>0.4023141535192251</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1228</v>
+        <v>0.4486</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.145879134570029</v>
+        <v>11.50490135032325</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -4592,43 +4713,43 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>0.1106</v>
+        <v>0.3518</v>
       </c>
       <c r="T8" t="n">
-        <v>7.101512766421464</v>
+        <v>12.55589769272465</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1275093671028546</v>
+        <v>0.4528283070384502</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1359640506542819</v>
+        <v>0.5033424605576753</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1444187342057091</v>
+        <v>0.5538566140769005</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>2</v>
+        <v>1.999999999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.08146639511201863</v>
+        <v>0.2229157378510925</v>
       </c>
       <c r="AA8" t="n">
-        <v>12477.055833</v>
+        <v>10194.378273</v>
       </c>
       <c r="AB8" t="n">
-        <v>3565.75736</v>
+        <v>6876.836912</v>
       </c>
       <c r="AC8" t="n">
-        <v>75.454998</v>
+        <v>49.057711</v>
       </c>
       <c r="AD8" t="n">
-        <v>2144.978265</v>
+        <v>255.691991</v>
       </c>
       <c r="AE8" t="n">
-        <v>58110891.25980759</v>
+        <v>39180178.05127673</v>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
@@ -4639,16 +4760,16 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ZKUSDT</t>
+          <t>NEOUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ZKsync</t>
+          <t>Neo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4658,7 +4779,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4672,10 +4793,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>66.392</v>
+        <v>62.24</v>
       </c>
       <c r="I9" t="n">
-        <v>82.98999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -4687,25 +4808,25 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N9" t="b">
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01959585256778836</v>
+        <v>2.663747724979867</v>
       </c>
       <c r="P9" t="n">
-        <v>0.02087</v>
+        <v>2.873</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.50212807941859</v>
+        <v>7.855559032780213</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -4713,19 +4834,19 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>0.01778</v>
+        <v>2.419</v>
       </c>
       <c r="T9" t="n">
-        <v>9.266514745948117</v>
+        <v>9.188097006510514</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02141170513557672</v>
+        <v>2.908495449959734</v>
       </c>
       <c r="V9" t="n">
-        <v>0.02322755770336508</v>
+        <v>3.153243174939601</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02504341027115345</v>
+        <v>3.397990899919468</v>
       </c>
       <c r="X9" t="n">
         <v>1</v>
@@ -4734,22 +4855,22 @@
         <v>2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.04783544606554921</v>
+        <v>0.03480076561683974</v>
       </c>
       <c r="AA9" t="n">
-        <v>47274.4740612</v>
+        <v>23935.640413</v>
       </c>
       <c r="AB9" t="n">
-        <v>58380.6843272</v>
+        <v>12162.162051</v>
       </c>
       <c r="AC9" t="n">
-        <v>22.622443</v>
+        <v>16.127085</v>
       </c>
       <c r="AD9" t="n">
-        <v>39.779511</v>
+        <v>581.822193</v>
       </c>
       <c r="AE9" t="n">
-        <v>193921738.6876874</v>
+        <v>201976367.3374268</v>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
@@ -4760,16 +4881,16 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MUSDT</t>
+          <t>DEXEUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MemeCore</t>
+          <t>DeXe</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4784,19 +4905,19 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>breakout</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>fresh_breakout</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>66.03616599999999</v>
+        <v>61.2</v>
       </c>
       <c r="I10" t="n">
-        <v>66.03616599999999</v>
+        <v>68</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
@@ -4816,13 +4937,13 @@
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.56624</v>
+        <v>5.160273207392032</v>
       </c>
       <c r="P10" t="n">
-        <v>1.74695</v>
+        <v>5.652</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.5378230667075</v>
+        <v>9.529084465984772</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -4830,19 +4951,19 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>1.485268466728675</v>
+        <v>4.79281843420018</v>
       </c>
       <c r="T10" t="n">
-        <v>5.169803687259019</v>
+        <v>7.120839506433045</v>
       </c>
       <c r="U10" t="n">
-        <v>1.647211533271326</v>
+        <v>5.527727980583883</v>
       </c>
       <c r="V10" t="n">
-        <v>1.728183066542652</v>
+        <v>5.895182753775734</v>
       </c>
       <c r="W10" t="n">
-        <v>1.809154599813977</v>
+        <v>6.262637526967586</v>
       </c>
       <c r="X10" t="n">
         <v>1</v>
@@ -4851,22 +4972,22 @@
         <v>2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.1257796911536845</v>
+        <v>0.07090941322459776</v>
       </c>
       <c r="AA10" t="n">
-        <v>4020.179897</v>
+        <v>3117.51048</v>
       </c>
       <c r="AB10" t="n">
-        <v>6949.0029706</v>
+        <v>1664.1054</v>
       </c>
       <c r="AC10" t="n">
-        <v>22.15674</v>
+        <v>125.532636</v>
       </c>
       <c r="AD10" t="n">
-        <v>1051.641306</v>
+        <v>226.913423</v>
       </c>
       <c r="AE10" t="n">
-        <v>2233919070.459943</v>
+        <v>471213956.3932709</v>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
@@ -4877,16 +4998,16 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BONKUSDT</t>
+          <t>HYPERUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bonk</t>
+          <t>Hyperlane</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4896,7 +5017,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4910,10 +5031,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>65.72799999999999</v>
+        <v>61.072</v>
       </c>
       <c r="I11" t="n">
-        <v>82.16</v>
+        <v>76.34</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -4925,25 +5046,25 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N11" t="b">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>6.116580042993848e-06</v>
+        <v>0.0923388600951853</v>
       </c>
       <c r="P11" t="n">
-        <v>6.426e-06</v>
+        <v>0.10873</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.058708540249923</v>
+        <v>17.75107456158576</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -4951,19 +5072,19 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>5.135e-06</v>
+        <v>0.07989</v>
       </c>
       <c r="T11" t="n">
-        <v>16.04785739897551</v>
+        <v>13.48171298882473</v>
       </c>
       <c r="U11" t="n">
-        <v>7.098160085987695e-06</v>
+        <v>0.1047877201903706</v>
       </c>
       <c r="V11" t="n">
-        <v>8.079740128981543e-06</v>
+        <v>0.1172365802855559</v>
       </c>
       <c r="W11" t="n">
-        <v>9.061320171975392e-06</v>
+        <v>0.1296854403807412</v>
       </c>
       <c r="X11" t="n">
         <v>1</v>
@@ -4972,22 +5093,22 @@
         <v>2</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.1243008079552479</v>
+        <v>0.1103549751701261</v>
       </c>
       <c r="AA11" t="n">
-        <v>141446.879968649</v>
+        <v>10067.1510832</v>
       </c>
       <c r="AB11" t="n">
-        <v>104208.376136778</v>
+        <v>9264.219072800001</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.21504</v>
+        <v>35.716808</v>
       </c>
       <c r="AD11" t="n">
-        <v>15.512563</v>
+        <v>149.145773</v>
       </c>
       <c r="AE11" t="n">
-        <v>566117408.0313501</v>
+        <v>25475599.87319592</v>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
@@ -4998,16 +5119,16 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RLCUSDT</t>
+          <t>ETHUSDT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iExec RLC</t>
+          <t>Ethereum</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5017,7 +5138,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>effective_rr_insufficient | entry_chased</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -5031,40 +5152,36 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>65.584</v>
+        <v>60.056</v>
       </c>
       <c r="I12" t="n">
-        <v>81.98</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="J12" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N12" t="b">
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4023141535192251</v>
+        <v>2080.287972457166</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4497</v>
+        <v>2337.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.77831952126698</v>
+        <v>12.36905807992079</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -5072,43 +5189,43 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>0.3518</v>
+        <v>1750</v>
       </c>
       <c r="T12" t="n">
-        <v>12.55589769272465</v>
+        <v>15.8770312971161</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4528283070384502</v>
+        <v>2410.575944914332</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5033424605576753</v>
+        <v>2740.863917371499</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5538566140769005</v>
+        <v>3071.151889828665</v>
       </c>
       <c r="X12" t="n">
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.999999999999999</v>
+        <v>2</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.2880248144455574</v>
+        <v>0.0004277004471701533</v>
       </c>
       <c r="AA12" t="n">
-        <v>6555.92775</v>
+        <v>266380.4482861</v>
       </c>
       <c r="AB12" t="n">
-        <v>8224.385313999999</v>
+        <v>602134.7222113</v>
       </c>
       <c r="AC12" t="n">
-        <v>35.660819</v>
+        <v>0.344305</v>
       </c>
       <c r="AD12" t="n">
-        <v>236.555748</v>
+        <v>0.42289</v>
       </c>
       <c r="AE12" t="n">
-        <v>39230827.60174326</v>
+        <v>282493405473.6589</v>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
@@ -5119,16 +5236,16 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ACHUSDT</t>
+          <t>ZETAUSDT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alchemy Pay</t>
+          <t>ZetaChain</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5152,10 +5269,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>63.152</v>
+        <v>59.312</v>
       </c>
       <c r="I13" t="n">
-        <v>78.94</v>
+        <v>74.14</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -5179,13 +5296,13 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.007042603236678154</v>
+        <v>0.05178030231565991</v>
       </c>
       <c r="P13" t="n">
-        <v>0.007514</v>
+        <v>0.0561</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.69350164250051</v>
+        <v>8.342357018324487</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -5193,43 +5310,43 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>0.006221</v>
+        <v>0.04527</v>
       </c>
       <c r="T13" t="n">
-        <v>11.66618662257178</v>
+        <v>12.57293222425046</v>
       </c>
       <c r="U13" t="n">
-        <v>0.007864206473356308</v>
+        <v>0.05829060463131982</v>
       </c>
       <c r="V13" t="n">
-        <v>0.008685809710034463</v>
+        <v>0.06480090694697974</v>
       </c>
       <c r="W13" t="n">
-        <v>0.009507412946712618</v>
+        <v>0.07131120926263965</v>
       </c>
       <c r="X13" t="n">
-        <v>0.9999999999999989</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>2</v>
+        <v>2.000000000000001</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.1998534408100645</v>
+        <v>0.05341404789460028</v>
       </c>
       <c r="AA13" t="n">
-        <v>17121.81179649</v>
+        <v>3140.8736058</v>
       </c>
       <c r="AB13" t="n">
-        <v>5001.72296197</v>
+        <v>3168.0047436</v>
       </c>
       <c r="AC13" t="n">
-        <v>67.692263</v>
+        <v>1620.676888</v>
       </c>
       <c r="AD13" t="n">
-        <v>278.244895</v>
+        <v>16346.801126</v>
       </c>
       <c r="AE13" t="n">
-        <v>75299172.72841798</v>
+        <v>73898404.18888804</v>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
@@ -5238,484 +5355,8 @@
       </c>
       <c r="AG13" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>14</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>NEOUSDT</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Neo</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>WAIT</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>reversal</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>reversal_base_reclaim</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>62.24</v>
-      </c>
-      <c r="I14" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>MARGINAL</t>
-        </is>
-      </c>
-      <c r="N14" t="b">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.663747724979867</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.823</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>5.978504402902352</v>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>chased</t>
-        </is>
-      </c>
-      <c r="S14" t="n">
-        <v>2.419</v>
-      </c>
-      <c r="T14" t="n">
-        <v>9.188097006510514</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.908495449959734</v>
-      </c>
-      <c r="V14" t="n">
-        <v>3.153243174939601</v>
-      </c>
-      <c r="W14" t="n">
-        <v>3.397990899919468</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0.03539196602370872</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>16729.029661</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>13607.129249</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>13.294779</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>78.45234000000001</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>199202098.8102723</v>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>RISK_OFF</t>
-        </is>
-      </c>
-      <c r="AG14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>15</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>BANUSDT</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Comedian</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>WAIT</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>tradeability_marginal | btc_regime_caution | entry_chased</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>pullback</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>pullback_to_ema</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="I15" t="n">
-        <v>68</v>
-      </c>
-      <c r="J15" t="b">
-        <v>1</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>MARGINAL</t>
-        </is>
-      </c>
-      <c r="N15" t="b">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.1355225963721603</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.16765</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>23.70630764748205</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>chased</t>
-        </is>
-      </c>
-      <c r="S15" t="n">
-        <v>0.1257953400014318</v>
-      </c>
-      <c r="T15" t="n">
-        <v>7.177590033780329</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.1452498527428888</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.1549771091136174</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0.1647043654843459</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0.09524376450978837</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>242.8176689</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>38.43508050000001</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>606.417869</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1961.302199</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>167369038.0239686</v>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>RISK_OFF</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>16</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>DEXEUSDT</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>DeXe</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>WAIT</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>tradeability_marginal | btc_regime_caution | entry_chased</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>pullback</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>pullback_to_ema</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="I16" t="n">
-        <v>68</v>
-      </c>
-      <c r="J16" t="b">
-        <v>1</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>MARGINAL</t>
-        </is>
-      </c>
-      <c r="N16" t="b">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>5.124723018133185</v>
-      </c>
-      <c r="P16" t="n">
-        <v>5.423</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5.820353232972786</v>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>chased</t>
-        </is>
-      </c>
-      <c r="S16" t="n">
-        <v>4.764082143488518</v>
-      </c>
-      <c r="T16" t="n">
-        <v>7.037275446274556</v>
-      </c>
-      <c r="U16" t="n">
-        <v>5.485363892777852</v>
-      </c>
-      <c r="V16" t="n">
-        <v>5.846004767422519</v>
-      </c>
-      <c r="W16" t="n">
-        <v>6.206645642067186</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0.01842468908337787</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1576.27559</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2078.82757</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>141.258695</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>528.480269</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>453479867.3362362</v>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>RISK_OFF</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>17</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>LAYERUSDT</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Solayer</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>WAIT</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>reversal</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>reversal_base_reclaim</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>61.168</v>
-      </c>
-      <c r="I17" t="n">
-        <v>76.45999999999999</v>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>MARGINAL</t>
-        </is>
-      </c>
-      <c r="N17" t="b">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.08553809548486238</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.08867999999999999</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.673105529563303</v>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>chased</t>
-        </is>
-      </c>
-      <c r="S17" t="n">
-        <v>0.07028</v>
-      </c>
-      <c r="T17" t="n">
-        <v>17.83777789109485</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.1007961909697248</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.1160542864545872</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.1313123819394496</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0.1465036344170903</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>5267.2081632</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>9429.638013100001</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>38.684651</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>135.465016</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>35323932.13587327</v>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>RISK_OFF</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AG17"/>
+  <autoFilter ref="A1:AG13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>